--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>당사자명</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -488,6 +493,11 @@
           <t>인도명령</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>주택</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -505,6 +515,11 @@
           <t>인도명령</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>주택</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -522,6 +537,11 @@
           <t>인도명령</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>주택</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -539,6 +559,11 @@
           <t>인도명령</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>주택</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -554,6 +579,11 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>인도명령</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>주택</t>
         </is>
       </c>
     </row>

--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조회대상" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,30 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,32 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,111 +415,106 @@
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>법원</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>사건번호</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>서울중앙지방법원</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2025타인12345</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>홍성지원</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024타인108</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUG가 임차보증금 권리승계 및 배당요구 신고</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>서울동부지방법원</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2025타인6789</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>홍성지원</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024타인109</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>동일 경매사건에서 HUG 권리승계 확인</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>인천지방법원</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2024타인3001</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>서울남부지방법원</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024타인220</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>임차권 승계인이 주택도시보증공사로 명시</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>수원지방법원</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2025타인8842</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>평택지원</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023타인84</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>해당 경매절차에 HUG가 유치권배제신청서 제출</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>의정부지방법원</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2025타인4521</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>평택지원</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023타인3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>해당 경매절차에 HUG가 유치권배제신청서 제출</t>
         </is>
       </c>
     </row>

--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -1,50 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조회대상" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="입력" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
       </patternFill>
     </fill>
   </fills>
@@ -57,104 +64,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -233,6 +162,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -267,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -301,20 +232,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -436,158 +363,79 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>법원</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>사건번호</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>당사자명</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>법원</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>사건번호</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>당사자명</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>서울중앙지방법원</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2025타인12345</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>서울동부지방법원</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2025타인6789</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>인천지방법원</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2024타인3001</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>수원지방법원</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2025타인8842</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>의정부지방법원</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2025타인4521</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>인도명령</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>주택</t>
-        </is>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>인천지방법원</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>2026타인50938</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>주택도시보증공사</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\전재룡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE7F576-7ADE-4CAB-827F-35B92AB170DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889BD2EF-0AAB-4E36-A80F-B4A5816DF0E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="10065" xr2:uid="{8D0F9930-D084-4684-8A7C-5888118A9192}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="304">
   <si>
     <t>법원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -41,339 +41,913 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026타인50737</t>
-  </si>
-  <si>
-    <t>2026타인50738</t>
+    <t>2026타인50848</t>
+  </si>
+  <si>
+    <t>2026타인50849</t>
+  </si>
+  <si>
+    <t>2026타인50855</t>
+  </si>
+  <si>
+    <t>2026타인50856</t>
+  </si>
+  <si>
+    <t>2026타인50862</t>
+  </si>
+  <si>
+    <t>2026타인50863</t>
+  </si>
+  <si>
+    <t>2026타인50866</t>
+  </si>
+  <si>
+    <t>2026타인50867</t>
+  </si>
+  <si>
+    <t>2026타인50876</t>
+  </si>
+  <si>
+    <t>2026타인50877</t>
+  </si>
+  <si>
+    <t>2026타인50878</t>
+  </si>
+  <si>
+    <t>2026타인50883</t>
+  </si>
+  <si>
+    <t>2026타인50884</t>
+  </si>
+  <si>
+    <t>2026타인50887</t>
+  </si>
+  <si>
+    <t>2026타인50888</t>
+  </si>
+  <si>
+    <t>2026타인50890</t>
+  </si>
+  <si>
+    <t>2026타인50891</t>
+  </si>
+  <si>
+    <t>2026타인50895</t>
+  </si>
+  <si>
+    <t>2026타인50899</t>
+  </si>
+  <si>
+    <t>2026타인50900</t>
+  </si>
+  <si>
+    <t>2026타인50901</t>
+  </si>
+  <si>
+    <t>2026타인50902</t>
+  </si>
+  <si>
+    <t>2026타인50903</t>
+  </si>
+  <si>
+    <t>2026타인50904</t>
+  </si>
+  <si>
+    <t>2026타인50905</t>
+  </si>
+  <si>
+    <t>2026타인50906</t>
+  </si>
+  <si>
+    <t>2026타인50907</t>
+  </si>
+  <si>
+    <t>2026타인50908</t>
+  </si>
+  <si>
+    <t>2026타인50909</t>
+  </si>
+  <si>
+    <t>2026타인50911</t>
+  </si>
+  <si>
+    <t>2026타인50915</t>
+  </si>
+  <si>
+    <t>2026타인50913</t>
+  </si>
+  <si>
+    <t>2026타인50914</t>
+  </si>
+  <si>
+    <t>2026타인50912</t>
+  </si>
+  <si>
+    <t>2026타인50916</t>
+  </si>
+  <si>
+    <t>2026타인50917</t>
+  </si>
+  <si>
+    <t>2026타인50925</t>
+  </si>
+  <si>
+    <t>2026타인50926</t>
+  </si>
+  <si>
+    <t>2026타인50927</t>
+  </si>
+  <si>
+    <t>2026타인50928</t>
+  </si>
+  <si>
+    <t>2026타인50929</t>
+  </si>
+  <si>
+    <t>2026타인50932</t>
+  </si>
+  <si>
+    <t>2026타인50933</t>
+  </si>
+  <si>
+    <t>2026타인50934</t>
+  </si>
+  <si>
+    <t>2026타인50935</t>
+  </si>
+  <si>
+    <t>2026타인50936</t>
+  </si>
+  <si>
+    <t>2026타인50937</t>
+  </si>
+  <si>
+    <t>2026타인50938</t>
+  </si>
+  <si>
+    <t>2026타인50939</t>
+  </si>
+  <si>
+    <t>2026타인50940</t>
+  </si>
+  <si>
+    <t>2026타인50941</t>
+  </si>
+  <si>
+    <t>2026타인50942</t>
+  </si>
+  <si>
+    <t>2026타인50943</t>
+  </si>
+  <si>
+    <t>2026타인50944</t>
+  </si>
+  <si>
+    <t>2026타인50945</t>
+  </si>
+  <si>
+    <t>2026타인50946</t>
+  </si>
+  <si>
+    <t>2026타인50947</t>
+  </si>
+  <si>
+    <t>2026타인50948</t>
+  </si>
+  <si>
+    <t>2026타인50949</t>
+  </si>
+  <si>
+    <t>2026타인50950</t>
+  </si>
+  <si>
+    <t>2026타인50951</t>
+  </si>
+  <si>
+    <t>2026타인50953</t>
+  </si>
+  <si>
+    <t>2026타인50954</t>
+  </si>
+  <si>
+    <t>2026타인50955</t>
+  </si>
+  <si>
+    <t>2026타인50956</t>
+  </si>
+  <si>
+    <t>2026타인50957</t>
+  </si>
+  <si>
+    <t>2026타인50958</t>
+  </si>
+  <si>
+    <t>2026타인50959</t>
+  </si>
+  <si>
+    <t>2026타인50960</t>
+  </si>
+  <si>
+    <t>2026타인50961</t>
+  </si>
+  <si>
+    <t>2026타인50962</t>
+  </si>
+  <si>
+    <t>2026타인50963</t>
+  </si>
+  <si>
+    <t>2026타인50964</t>
+  </si>
+  <si>
+    <t>2026타인50965</t>
+  </si>
+  <si>
+    <t>2026타인50967</t>
+  </si>
+  <si>
+    <t>2026타인50968</t>
+  </si>
+  <si>
+    <t>2026타인50969</t>
+  </si>
+  <si>
+    <t>2026타인50970</t>
+  </si>
+  <si>
+    <t>2026타인50971</t>
+  </si>
+  <si>
+    <t>2026타인50972</t>
+  </si>
+  <si>
+    <t>2026타인50973</t>
+  </si>
+  <si>
+    <t>2026타인50974</t>
+  </si>
+  <si>
+    <t>2026타인50976</t>
+  </si>
+  <si>
+    <t>2026타인50977</t>
+  </si>
+  <si>
+    <t>인천지방법원</t>
+  </si>
+  <si>
+    <t>주택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울중앙지방법원</t>
+  </si>
+  <si>
+    <t>서울북부지방법원</t>
+  </si>
+  <si>
+    <t>서울남부지방법원</t>
+  </si>
+  <si>
+    <t>인천지방법원 부천지원</t>
+  </si>
+  <si>
+    <t>의정부지방법원 고양지원</t>
+  </si>
+  <si>
+    <t>부산지방법원</t>
+  </si>
+  <si>
+    <t>서울서부지방법원</t>
+  </si>
+  <si>
+    <t>수원지방법원</t>
+  </si>
+  <si>
+    <t>서울남부지방법원</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2026타인50741</t>
-  </si>
-  <si>
-    <t>2026타인50742</t>
-  </si>
-  <si>
-    <t>2026타인50799</t>
-  </si>
-  <si>
-    <t>2026타인50800</t>
-  </si>
-  <si>
-    <t>2026타인50842</t>
-  </si>
-  <si>
-    <t>2026타인50843</t>
-  </si>
-  <si>
-    <t>2026타인50844</t>
-  </si>
-  <si>
-    <t>2026타인50846</t>
-  </si>
-  <si>
-    <t>2026타인50847</t>
-  </si>
-  <si>
-    <t>2026타인50848</t>
-  </si>
-  <si>
-    <t>2026타인50849</t>
-  </si>
-  <si>
-    <t>2026타인50855</t>
-  </si>
-  <si>
-    <t>2026타인50856</t>
-  </si>
-  <si>
-    <t>2026타인50859</t>
-  </si>
-  <si>
-    <t>2026타인50860</t>
-  </si>
-  <si>
-    <t>2026타인50862</t>
-  </si>
-  <si>
-    <t>2026타인50863</t>
-  </si>
-  <si>
-    <t>2026타인50864</t>
-  </si>
-  <si>
-    <t>2026타인50865</t>
-  </si>
-  <si>
-    <t>2026타인50866</t>
-  </si>
-  <si>
-    <t>2026타인50867</t>
-  </si>
-  <si>
-    <t>2026타인50868</t>
-  </si>
-  <si>
-    <t>2026타인50869</t>
-  </si>
-  <si>
-    <t>2026타인50873</t>
-  </si>
-  <si>
-    <t>2026타인50876</t>
-  </si>
-  <si>
-    <t>2026타인50877</t>
-  </si>
-  <si>
-    <t>2026타인50878</t>
-  </si>
-  <si>
-    <t>2026타인50883</t>
-  </si>
-  <si>
-    <t>2026타인50884</t>
-  </si>
-  <si>
-    <t>2026타인50885</t>
-  </si>
-  <si>
-    <t>2026타인50886</t>
-  </si>
-  <si>
-    <t>2026타인50887</t>
-  </si>
-  <si>
-    <t>2026타인50888</t>
-  </si>
-  <si>
-    <t>2026타인50890</t>
-  </si>
-  <si>
-    <t>2026타인50891</t>
-  </si>
-  <si>
-    <t>2026타인50892</t>
-  </si>
-  <si>
-    <t>2026타인50893</t>
-  </si>
-  <si>
-    <t>2026타인50894</t>
-  </si>
-  <si>
-    <t>2026타인50895</t>
-  </si>
-  <si>
-    <t>2026타인50896</t>
-  </si>
-  <si>
-    <t>2026타인50899</t>
-  </si>
-  <si>
-    <t>2026타인50900</t>
-  </si>
-  <si>
-    <t>2026타인50901</t>
-  </si>
-  <si>
-    <t>2026타인50902</t>
-  </si>
-  <si>
-    <t>2026타인50903</t>
-  </si>
-  <si>
-    <t>2026타인50904</t>
-  </si>
-  <si>
-    <t>2026타인50905</t>
-  </si>
-  <si>
-    <t>2026타인50906</t>
-  </si>
-  <si>
-    <t>2026타인50907</t>
-  </si>
-  <si>
-    <t>2026타인50908</t>
-  </si>
-  <si>
-    <t>2026타인50909</t>
-  </si>
-  <si>
-    <t>2026타인50911</t>
-  </si>
-  <si>
-    <t>2026타인50915</t>
-  </si>
-  <si>
-    <t>2026타인50913</t>
-  </si>
-  <si>
-    <t>2026타인50914</t>
-  </si>
-  <si>
-    <t>2026타인50912</t>
-  </si>
-  <si>
-    <t>2026타인50916</t>
-  </si>
-  <si>
-    <t>2026타인50917</t>
-  </si>
-  <si>
-    <t>2026타인50925</t>
-  </si>
-  <si>
-    <t>2026타인50926</t>
-  </si>
-  <si>
-    <t>2026타인50927</t>
-  </si>
-  <si>
-    <t>2026타인50928</t>
-  </si>
-  <si>
-    <t>2026타인50929</t>
-  </si>
-  <si>
-    <t>2026타인50932</t>
-  </si>
-  <si>
-    <t>2026타인50933</t>
-  </si>
-  <si>
-    <t>2026타인50934</t>
-  </si>
-  <si>
-    <t>2026타인50935</t>
-  </si>
-  <si>
-    <t>2026타인50936</t>
-  </si>
-  <si>
-    <t>2026타인50937</t>
-  </si>
-  <si>
-    <t>2026타인50938</t>
-  </si>
-  <si>
-    <t>2026타인50939</t>
-  </si>
-  <si>
-    <t>2026타인50940</t>
-  </si>
-  <si>
-    <t>2026타인50941</t>
-  </si>
-  <si>
-    <t>2026타인50942</t>
-  </si>
-  <si>
-    <t>2026타인50943</t>
-  </si>
-  <si>
-    <t>2026타인50944</t>
-  </si>
-  <si>
-    <t>2026타인50945</t>
-  </si>
-  <si>
-    <t>2026타인50946</t>
-  </si>
-  <si>
-    <t>2026타인50947</t>
-  </si>
-  <si>
-    <t>2026타인50948</t>
-  </si>
-  <si>
-    <t>2026타인50949</t>
-  </si>
-  <si>
-    <t>2026타인50950</t>
-  </si>
-  <si>
-    <t>2026타인50951</t>
-  </si>
-  <si>
-    <t>2026타인50953</t>
-  </si>
-  <si>
-    <t>2026타인50954</t>
-  </si>
-  <si>
-    <t>2026타인50955</t>
-  </si>
-  <si>
-    <t>2026타인50956</t>
-  </si>
-  <si>
-    <t>2026타인50957</t>
-  </si>
-  <si>
-    <t>2026타인50958</t>
-  </si>
-  <si>
-    <t>2026타인50959</t>
-  </si>
-  <si>
-    <t>2026타인50960</t>
-  </si>
-  <si>
-    <t>2026타인50961</t>
-  </si>
-  <si>
-    <t>2026타인50962</t>
-  </si>
-  <si>
-    <t>2026타인50963</t>
-  </si>
-  <si>
-    <t>2026타인50964</t>
-  </si>
-  <si>
-    <t>2026타인50965</t>
-  </si>
-  <si>
-    <t>2026타인50967</t>
-  </si>
-  <si>
-    <t>2026타인50968</t>
-  </si>
-  <si>
-    <t>2026타인50969</t>
-  </si>
-  <si>
-    <t>2026타인50970</t>
-  </si>
-  <si>
-    <t>2026타인50971</t>
-  </si>
-  <si>
-    <t>2026타인50972</t>
-  </si>
-  <si>
-    <t>2026타인50973</t>
-  </si>
-  <si>
-    <t>2026타인50974</t>
-  </si>
-  <si>
-    <t>2026타인50976</t>
-  </si>
-  <si>
-    <t>2026타인50977</t>
+    <t>인천지방법원</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026타인10192</t>
+  </si>
+  <si>
+    <t>2026타인10195</t>
+  </si>
+  <si>
+    <t>2026타인10007</t>
+  </si>
+  <si>
+    <t>2026타인10046</t>
+  </si>
+  <si>
+    <t>2026타인5044</t>
+  </si>
+  <si>
+    <t>2026타인10233</t>
+  </si>
+  <si>
+    <t>2026타인10234</t>
+  </si>
+  <si>
+    <t>2026타인4113</t>
+  </si>
+  <si>
+    <t>2026타인4134</t>
+  </si>
+  <si>
+    <t>2026타인4154</t>
+  </si>
+  <si>
+    <t>2026타인4159</t>
+  </si>
+  <si>
+    <t>2026타인4161</t>
+  </si>
+  <si>
+    <t>2026타인4175</t>
+  </si>
+  <si>
+    <t>2026타인4173</t>
+  </si>
+  <si>
+    <t>2026타인4171</t>
+  </si>
+  <si>
+    <t>2026타인4162</t>
+  </si>
+  <si>
+    <t>2026타인4156</t>
+  </si>
+  <si>
+    <t>2026타인4153</t>
+  </si>
+  <si>
+    <t>2026타인10240</t>
+  </si>
+  <si>
+    <t>2026타인10338</t>
+  </si>
+  <si>
+    <t>2026타인10339</t>
+  </si>
+  <si>
+    <t>2026타인10342</t>
+  </si>
+  <si>
+    <t>2026타인10343</t>
+  </si>
+  <si>
+    <t>2026타인10344</t>
+  </si>
+  <si>
+    <t>2026타인10345</t>
+  </si>
+  <si>
+    <t>2026타인10241</t>
+  </si>
+  <si>
+    <t>2026타인4197</t>
+  </si>
+  <si>
+    <t>2026타인4198</t>
+  </si>
+  <si>
+    <t>2026타인4199</t>
+  </si>
+  <si>
+    <t>2026타인4201</t>
+  </si>
+  <si>
+    <t>2026타인4202</t>
+  </si>
+  <si>
+    <t>2026타인4203</t>
+  </si>
+  <si>
+    <t>2026타인4204</t>
+  </si>
+  <si>
+    <t>2026타인4205</t>
+  </si>
+  <si>
+    <t>2026타인4210</t>
+  </si>
+  <si>
+    <t>2026타인4211</t>
+  </si>
+  <si>
+    <t>2026타인4214</t>
+  </si>
+  <si>
+    <t>2026타인4215</t>
+  </si>
+  <si>
+    <t>2026타인4216</t>
+  </si>
+  <si>
+    <t>2026타인4217</t>
+  </si>
+  <si>
+    <t>2026타인4218</t>
+  </si>
+  <si>
+    <t>2026타인4221</t>
+  </si>
+  <si>
+    <t>2026타인4224</t>
+  </si>
+  <si>
+    <t>2026타인4225</t>
+  </si>
+  <si>
+    <t>2026타인10154</t>
+  </si>
+  <si>
+    <t>2026타인10164</t>
+  </si>
+  <si>
+    <t>2026타인10352</t>
+  </si>
+  <si>
+    <t>2026타인10355</t>
+  </si>
+  <si>
+    <t>2026타인10356</t>
+  </si>
+  <si>
+    <t>2026타인10358</t>
+  </si>
+  <si>
+    <t>2026타인10353</t>
+  </si>
+  <si>
+    <t>2026타인10354</t>
+  </si>
+  <si>
+    <t>2026타인10363</t>
+  </si>
+  <si>
+    <t>2026타인10364</t>
+  </si>
+  <si>
+    <t>2026타인10365</t>
+  </si>
+  <si>
+    <t>2026타인3783</t>
+  </si>
+  <si>
+    <t>2026타인3784</t>
+  </si>
+  <si>
+    <t>2026타인3939</t>
+  </si>
+  <si>
+    <t>2026타인3928</t>
+  </si>
+  <si>
+    <t>2026타인3966</t>
+  </si>
+  <si>
+    <t>2026타인3968</t>
+  </si>
+  <si>
+    <t>2026타인3975</t>
+  </si>
+  <si>
+    <t>2026타인3989</t>
+  </si>
+  <si>
+    <t>2026타인3996</t>
+  </si>
+  <si>
+    <t>2026타인4000</t>
+  </si>
+  <si>
+    <t>2026타인4004</t>
+  </si>
+  <si>
+    <t>2026타인4007</t>
+  </si>
+  <si>
+    <t>2026타인4017</t>
+  </si>
+  <si>
+    <t>2026타인4032</t>
+  </si>
+  <si>
+    <t>2026타인4035</t>
+  </si>
+  <si>
+    <t>2026타인4053</t>
+  </si>
+  <si>
+    <t>2026타인4060</t>
+  </si>
+  <si>
+    <t>2026타인4026</t>
+  </si>
+  <si>
+    <t>2026타인4069</t>
+  </si>
+  <si>
+    <t>2026타인4089</t>
+  </si>
+  <si>
+    <t>2026타인4091</t>
+  </si>
+  <si>
+    <t>2026타인4118</t>
+  </si>
+  <si>
+    <t>2026타인4123</t>
+  </si>
+  <si>
+    <t>2026타인4127</t>
+  </si>
+  <si>
+    <t>2026타인4133</t>
+  </si>
+  <si>
+    <t>2026타인4167</t>
+  </si>
+  <si>
+    <t>2026타인4169</t>
+  </si>
+  <si>
+    <t>2026타인4176</t>
+  </si>
+  <si>
+    <t>2026타인4179</t>
+  </si>
+  <si>
+    <t>2026타인4182</t>
+  </si>
+  <si>
+    <t>2026타인4184</t>
+  </si>
+  <si>
+    <t>2026타인4186</t>
+  </si>
+  <si>
+    <t>2026타인4188</t>
+  </si>
+  <si>
+    <t>2026타인4190</t>
+  </si>
+  <si>
+    <t>2026타인4192</t>
+  </si>
+  <si>
+    <t>2026타인4135</t>
+  </si>
+  <si>
+    <t>2026타인4139</t>
+  </si>
+  <si>
+    <t>2026타인4141</t>
+  </si>
+  <si>
+    <t>2026타인4144</t>
+  </si>
+  <si>
+    <t>2026타인4149</t>
+  </si>
+  <si>
+    <t>2026타인4151</t>
+  </si>
+  <si>
+    <t>2026타인4155</t>
+  </si>
+  <si>
+    <t>2026타인4166</t>
+  </si>
+  <si>
+    <t>2026타인4164</t>
+  </si>
+  <si>
+    <t>2026타인4158</t>
+  </si>
+  <si>
+    <t>2026타인4206</t>
+  </si>
+  <si>
+    <t>2026타인4208</t>
+  </si>
+  <si>
+    <t>2026타인4212</t>
+  </si>
+  <si>
+    <t>2026타인4219</t>
+  </si>
+  <si>
+    <t>2026타인4227</t>
+  </si>
+  <si>
+    <t>2026타인4229</t>
+  </si>
+  <si>
+    <t>2026타인3782</t>
+  </si>
+  <si>
+    <t>2026타인3785</t>
+  </si>
+  <si>
+    <t>2026타인4100</t>
+  </si>
+  <si>
+    <t>2026타인3931</t>
+  </si>
+  <si>
+    <t>2026타인3967</t>
+  </si>
+  <si>
+    <t>2026타인3969</t>
+  </si>
+  <si>
+    <t>2026타인3976</t>
+  </si>
+  <si>
+    <t>2026타인3990</t>
+  </si>
+  <si>
+    <t>2026타인3997</t>
+  </si>
+  <si>
+    <t>2026타인4001</t>
+  </si>
+  <si>
+    <t>2026타인4005</t>
+  </si>
+  <si>
+    <t>2026타인4008</t>
+  </si>
+  <si>
+    <t>2026타인4019</t>
+  </si>
+  <si>
+    <t>2026타인4033</t>
+  </si>
+  <si>
+    <t>2026타인4036</t>
+  </si>
+  <si>
+    <t>2026타인4052</t>
+  </si>
+  <si>
+    <t>2026타인4061</t>
+  </si>
+  <si>
+    <t>2026타인4027</t>
+  </si>
+  <si>
+    <t>2026타인4070</t>
+  </si>
+  <si>
+    <t>2026타인4090</t>
+  </si>
+  <si>
+    <t>2026타인4092</t>
+  </si>
+  <si>
+    <t>2026타인4119</t>
+  </si>
+  <si>
+    <t>2026타인4124</t>
+  </si>
+  <si>
+    <t>2026타인4128</t>
+  </si>
+  <si>
+    <t>2026타인4136</t>
+  </si>
+  <si>
+    <t>2026타인4168</t>
+  </si>
+  <si>
+    <t>2026타인4172</t>
+  </si>
+  <si>
+    <t>2026타인4177</t>
+  </si>
+  <si>
+    <t>2026타인4180</t>
+  </si>
+  <si>
+    <t>2026타인4183</t>
+  </si>
+  <si>
+    <t>2026타인4185</t>
+  </si>
+  <si>
+    <t>2026타인4187</t>
+  </si>
+  <si>
+    <t>2026타인4189</t>
+  </si>
+  <si>
+    <t>2026타인4191</t>
+  </si>
+  <si>
+    <t>2026타인4193</t>
+  </si>
+  <si>
+    <t>2026타인4137</t>
+  </si>
+  <si>
+    <t>2026타인4140</t>
+  </si>
+  <si>
+    <t>2026타인4142</t>
+  </si>
+  <si>
+    <t>2026타인4146</t>
+  </si>
+  <si>
+    <t>2026타인4150</t>
+  </si>
+  <si>
+    <t>2026타인4152</t>
+  </si>
+  <si>
+    <t>2206타인4157</t>
+  </si>
+  <si>
+    <t>2026타인4170</t>
+  </si>
+  <si>
+    <t>2026타인4165</t>
+  </si>
+  <si>
+    <t>2026타인4160</t>
+  </si>
+  <si>
+    <t>2026타인4207</t>
+  </si>
+  <si>
+    <t>2026타인4209</t>
+  </si>
+  <si>
+    <t>2026타인4213</t>
+  </si>
+  <si>
+    <t>2026타인4220</t>
+  </si>
+  <si>
+    <t>2026타인4228</t>
+  </si>
+  <si>
+    <t>2026타인4230</t>
+  </si>
+  <si>
+    <t>2026타인10330</t>
+  </si>
+  <si>
+    <t>2026타인10301</t>
+  </si>
+  <si>
+    <t>2026타인10194</t>
+  </si>
+  <si>
+    <t>2026타인10197</t>
+  </si>
+  <si>
+    <t>2026타인2101</t>
+  </si>
+  <si>
+    <t>2026타인10144</t>
+  </si>
+  <si>
+    <t>2026타인100238</t>
+  </si>
+  <si>
+    <t>2026타인10236</t>
+  </si>
+  <si>
+    <t>2026타인10239</t>
+  </si>
+  <si>
+    <t>2026타인10348</t>
+  </si>
+  <si>
+    <t>2026타인10341</t>
+  </si>
+  <si>
+    <t>2026타인10085</t>
+  </si>
+  <si>
+    <t>2026타인10075</t>
+  </si>
+  <si>
+    <t>2026타인10300</t>
+  </si>
+  <si>
+    <t>2026타인10193</t>
+  </si>
+  <si>
+    <t>2026타인10196</t>
+  </si>
+  <si>
+    <t>2026타인2103</t>
+  </si>
+  <si>
+    <t>2026타인10143</t>
+  </si>
+  <si>
+    <t>2026타인100237</t>
+  </si>
+  <si>
+    <t>2026타인10235</t>
+  </si>
+  <si>
+    <t>2026타인10238</t>
+  </si>
+  <si>
+    <t>2026타인10347</t>
+  </si>
+  <si>
+    <t>2026타인10340</t>
+  </si>
+  <si>
+    <t>2026타인10242</t>
+  </si>
+  <si>
+    <t>2026타인10151</t>
+  </si>
+  <si>
+    <t>2026타인10155</t>
+  </si>
+  <si>
+    <t>2026타인10157</t>
+  </si>
+  <si>
+    <t>2026타인10160</t>
+  </si>
+  <si>
+    <t>2026타인10162</t>
   </si>
   <si>
     <t>2026타인50875</t>
+  </si>
+  <si>
+    <t>2026타인10340.</t>
+  </si>
+  <si>
+    <t>2026타인10346</t>
+  </si>
+  <si>
+    <t>2026타인10359</t>
+  </si>
+  <si>
+    <t>2026타인10361</t>
+  </si>
+  <si>
+    <t>2026타인10357</t>
+  </si>
+  <si>
+    <t>2026타인10133</t>
+  </si>
+  <si>
+    <t>2026타인10243</t>
+  </si>
+  <si>
+    <t>2026타인10152</t>
+  </si>
+  <si>
+    <t>2026타인10156</t>
+  </si>
+  <si>
+    <t>2026타인10158</t>
+  </si>
+  <si>
+    <t>2026타인10161</t>
+  </si>
+  <si>
+    <t>2026타인10163</t>
+  </si>
+  <si>
+    <t>2026타인10360</t>
+  </si>
+  <si>
+    <t>2026타인10362</t>
+  </si>
+  <si>
+    <t>2026타인4233</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>인천지방법원</t>
-  </si>
-  <si>
-    <t>주택</t>
+    <t>2026타인4240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026타인10360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026타인10342</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -381,7 +955,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +991,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -446,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -469,6 +1050,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -788,8 +1375,8 @@
   <dimension ref="A1:H444"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
@@ -808,1928 +1395,3407 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>94</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
+      <c r="A4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4" t="s">
-        <v>112</v>
+      <c r="A5" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
+      <c r="A6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
+      <c r="A7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
+      <c r="A8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
+      <c r="A9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>11</v>
+      <c r="A10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>91</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>91</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>91</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>91</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>19</v>
+        <v>91</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>91</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>91</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>22</v>
+        <v>91</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>23</v>
+        <v>91</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>91</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>26</v>
+        <v>91</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>91</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>91</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>91</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>91</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>30</v>
+        <v>91</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>31</v>
+        <v>91</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>32</v>
+        <v>91</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>91</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>91</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>36</v>
+        <v>91</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>37</v>
+        <v>91</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>38</v>
+        <v>91</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>39</v>
+        <v>91</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>40</v>
+        <v>91</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>41</v>
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>42</v>
+        <v>91</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>43</v>
+        <v>91</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>44</v>
+        <v>91</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>45</v>
+      <c r="A45" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>48</v>
+        <v>91</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>91</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>52</v>
+        <v>91</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>56</v>
+        <v>91</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>60</v>
+        <v>91</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>59</v>
+        <v>91</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>57</v>
+        <v>191</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>61</v>
+        <v>91</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>63</v>
+        <v>91</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>65</v>
+        <v>91</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>74</v>
+        <v>91</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>78</v>
+        <v>91</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>81</v>
+        <v>91</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>86</v>
-      </c>
       <c r="C86" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>91</v>
+        <v>91</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="4" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="7"/>
+      <c r="A111" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="7"/>
+      <c r="A112" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="7"/>
+      <c r="A113" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="7"/>
+      <c r="A114" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="7"/>
+      <c r="A115" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="7"/>
+      <c r="A116" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="7"/>
+      <c r="A117" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="7"/>
+      <c r="A118" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="7"/>
+      <c r="A119" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="7"/>
+      <c r="A120" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="7"/>
+      <c r="A121" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="7"/>
+      <c r="A122" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="7"/>
+      <c r="A123" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="7"/>
+      <c r="A124" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="7"/>
+      <c r="A125" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="7"/>
+      <c r="A126" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="7"/>
+      <c r="A127" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="7"/>
+      <c r="A128" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="7"/>
+      <c r="A129" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="7"/>
+      <c r="A130" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="7"/>
+      <c r="A131" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="7"/>
+      <c r="A132" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="7"/>
+      <c r="A133" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="4"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="7"/>
+      <c r="A134" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="4"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="7"/>
+      <c r="A135" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="7"/>
+      <c r="A136" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="7"/>
+      <c r="A137" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="7"/>
+      <c r="A138" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="7"/>
+      <c r="A139" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="7"/>
+      <c r="A140" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="7"/>
+      <c r="A141" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="142" spans="1:3">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="7"/>
+      <c r="A142" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="4"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="7"/>
+      <c r="A143" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="4"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="7"/>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="4"/>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="B146" s="4"/>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="B147" s="4"/>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="4"/>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="B149" s="4"/>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="4"/>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="B151" s="4"/>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="4"/>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="B153" s="4"/>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="4"/>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="B155" s="4"/>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="B156" s="4"/>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="B157" s="4"/>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="B158" s="4"/>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="B159" s="4"/>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="B160" s="4"/>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="4"/>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="B162" s="4"/>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="B163" s="4"/>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="B164" s="4"/>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="4"/>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="B166" s="4"/>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="B167" s="4"/>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="4"/>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="B169" s="4"/>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="4"/>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="B171" s="4"/>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="4"/>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="B173" s="4"/>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="B174" s="4"/>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="B175" s="4"/>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="4"/>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="B177" s="4"/>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="4"/>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="B179" s="4"/>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="B180" s="4"/>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="4"/>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="B182" s="4"/>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="4"/>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="B184" s="4"/>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="4"/>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="B186" s="4"/>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="4"/>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="B188" s="4"/>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="4"/>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="B190" s="4"/>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="4"/>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="B192" s="4"/>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="B193" s="4"/>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="B194" s="4"/>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="B195" s="4"/>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="B196" s="4"/>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="B197" s="4"/>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="B198" s="4"/>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="B199" s="4"/>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="B200" s="4"/>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="B201" s="4"/>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="4"/>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="B203" s="4"/>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="4"/>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="B205" s="4"/>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="B206" s="4"/>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="B207" s="4"/>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="4"/>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="B209" s="4"/>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="B210" s="4"/>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="B211" s="4"/>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="B212" s="4"/>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="B213" s="4"/>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="B214" s="4"/>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="4"/>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="B216" s="4"/>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="B217" s="4"/>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="B218" s="4"/>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="B219" s="4"/>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="4"/>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="B221" s="4"/>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="4"/>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="B223" s="4"/>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="2"/>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="4"/>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="B226" s="3"/>
-    </row>
-    <row r="227" spans="1:2">
-      <c r="B227" s="3"/>
-    </row>
-    <row r="228" spans="1:2">
-      <c r="A228" s="3"/>
-    </row>
-    <row r="229" spans="1:2">
-      <c r="A229" s="3"/>
-    </row>
-    <row r="230" spans="1:2">
-      <c r="B230" s="4"/>
-    </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="4"/>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="B232" s="4"/>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="B233" s="4"/>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" s="4"/>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="B235" s="4"/>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="B236" s="4"/>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" s="4"/>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="B238" s="4"/>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" s="4"/>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="B240" s="4"/>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="B241" s="4"/>
-    </row>
-    <row r="242" spans="1:2">
-      <c r="A242" s="4"/>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="B243" s="4"/>
-    </row>
-    <row r="244" spans="1:2">
-      <c r="A244" s="4"/>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="B245" s="4"/>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="B246" s="4"/>
-    </row>
-    <row r="247" spans="1:2">
-      <c r="B247" s="4"/>
-    </row>
-    <row r="248" spans="1:2">
-      <c r="B248" s="4"/>
-    </row>
-    <row r="249" spans="1:2">
-      <c r="B249" s="4"/>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="B250" s="4"/>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251" s="4"/>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="B252" s="2"/>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="B253" s="3"/>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="B254" s="3"/>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255" s="3"/>
-    </row>
-    <row r="256" spans="1:2">
-      <c r="B256" s="2"/>
-    </row>
-    <row r="257" spans="1:2">
-      <c r="B257" s="2"/>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258" s="2"/>
-    </row>
-    <row r="259" spans="1:2">
-      <c r="B259" s="2"/>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="B260" s="2"/>
-    </row>
-    <row r="261" spans="1:2">
-      <c r="A261" s="2"/>
-    </row>
-    <row r="262" spans="1:2">
-      <c r="B262" s="4"/>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="B263" s="4"/>
-    </row>
-    <row r="264" spans="1:2">
-      <c r="B264" s="4"/>
-    </row>
-    <row r="265" spans="1:2">
-      <c r="A265" s="4"/>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="B266" s="4"/>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" s="4"/>
-    </row>
-    <row r="268" spans="1:2">
-      <c r="B268" s="4"/>
-    </row>
-    <row r="269" spans="1:2">
-      <c r="B269" s="4"/>
-    </row>
-    <row r="270" spans="1:2">
-      <c r="B270" s="4"/>
-    </row>
-    <row r="271" spans="1:2">
-      <c r="A271" s="4"/>
-    </row>
-    <row r="272" spans="1:2">
-      <c r="B272" s="4"/>
-    </row>
-    <row r="273" spans="1:2">
-      <c r="A273" s="4"/>
-    </row>
-    <row r="274" spans="1:2">
-      <c r="B274" s="4"/>
-    </row>
-    <row r="275" spans="1:2">
-      <c r="B275" s="3"/>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276" s="3"/>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="B277" s="3"/>
-    </row>
-    <row r="278" spans="1:2">
-      <c r="A278" s="3"/>
-    </row>
-    <row r="279" spans="1:2">
-      <c r="B279" s="3"/>
-    </row>
-    <row r="280" spans="1:2">
-      <c r="A280" s="3"/>
-    </row>
-    <row r="281" spans="1:2">
-      <c r="B281" s="4"/>
-    </row>
-    <row r="282" spans="1:2">
-      <c r="B282" s="4"/>
-    </row>
-    <row r="283" spans="1:2">
-      <c r="B283" s="4"/>
-    </row>
-    <row r="284" spans="1:2">
-      <c r="B284" s="4"/>
-    </row>
-    <row r="285" spans="1:2">
-      <c r="A285" s="4"/>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="B287" s="4"/>
-    </row>
-    <row r="288" spans="1:2">
-      <c r="B288" s="4"/>
-    </row>
-    <row r="289" spans="1:2">
-      <c r="B289" s="4"/>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="B290" s="4"/>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="4"/>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="B292" s="4"/>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="B293" s="4"/>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="B294" s="4"/>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="A295" s="4"/>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="B296" s="4"/>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="B297" s="4"/>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="B298" s="4"/>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="B299" s="4"/>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="B300" s="4"/>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" s="4"/>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="B302" s="4"/>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="4"/>
-    </row>
-    <row r="304" spans="1:2">
+      <c r="A144" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C252" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C253" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C255" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C268" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B281" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
       <c r="B304" s="3"/>
     </row>
     <row r="305" spans="1:2">
@@ -3159,8 +5225,8 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:C110">
-    <sortCondition ref="B5"/>
+  <sortState ref="A2:C303">
+    <sortCondition ref="A5"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\전재룡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889BD2EF-0AAB-4E36-A80F-B4A5816DF0E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F30E864-BB62-454E-AE57-1B84B9FCCC4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="10065" xr2:uid="{8D0F9930-D084-4684-8A7C-5888118A9192}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="인천남부법원" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">인천남부법원!$A$1:$C$360</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="226">
   <si>
     <t>법원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,28 +300,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>서울중앙지방법원</t>
-  </si>
-  <si>
-    <t>서울북부지방법원</t>
-  </si>
-  <si>
     <t>서울남부지방법원</t>
-  </si>
-  <si>
-    <t>인천지방법원 부천지원</t>
-  </si>
-  <si>
-    <t>의정부지방법원 고양지원</t>
-  </si>
-  <si>
-    <t>부산지방법원</t>
-  </si>
-  <si>
-    <t>서울서부지방법원</t>
-  </si>
-  <si>
-    <t>수원지방법원</t>
   </si>
   <si>
     <t>서울남부지방법원</t>
@@ -332,27 +311,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2026타인10192</t>
-  </si>
-  <si>
-    <t>2026타인10195</t>
-  </si>
-  <si>
-    <t>2026타인10007</t>
-  </si>
-  <si>
-    <t>2026타인10046</t>
-  </si>
-  <si>
-    <t>2026타인5044</t>
-  </si>
-  <si>
-    <t>2026타인10233</t>
-  </si>
-  <si>
-    <t>2026타인10234</t>
-  </si>
-  <si>
     <t>2026타인4113</t>
   </si>
   <si>
@@ -386,30 +344,6 @@
     <t>2026타인4153</t>
   </si>
   <si>
-    <t>2026타인10240</t>
-  </si>
-  <si>
-    <t>2026타인10338</t>
-  </si>
-  <si>
-    <t>2026타인10339</t>
-  </si>
-  <si>
-    <t>2026타인10342</t>
-  </si>
-  <si>
-    <t>2026타인10343</t>
-  </si>
-  <si>
-    <t>2026타인10344</t>
-  </si>
-  <si>
-    <t>2026타인10345</t>
-  </si>
-  <si>
-    <t>2026타인10241</t>
-  </si>
-  <si>
     <t>2026타인4197</t>
   </si>
   <si>
@@ -464,39 +398,6 @@
     <t>2026타인4225</t>
   </si>
   <si>
-    <t>2026타인10154</t>
-  </si>
-  <si>
-    <t>2026타인10164</t>
-  </si>
-  <si>
-    <t>2026타인10352</t>
-  </si>
-  <si>
-    <t>2026타인10355</t>
-  </si>
-  <si>
-    <t>2026타인10356</t>
-  </si>
-  <si>
-    <t>2026타인10358</t>
-  </si>
-  <si>
-    <t>2026타인10353</t>
-  </si>
-  <si>
-    <t>2026타인10354</t>
-  </si>
-  <si>
-    <t>2026타인10363</t>
-  </si>
-  <si>
-    <t>2026타인10364</t>
-  </si>
-  <si>
-    <t>2026타인10365</t>
-  </si>
-  <si>
     <t>2026타인3783</t>
   </si>
   <si>
@@ -803,136 +704,7 @@
     <t>2026타인4230</t>
   </si>
   <si>
-    <t>2026타인10330</t>
-  </si>
-  <si>
-    <t>2026타인10301</t>
-  </si>
-  <si>
-    <t>2026타인10194</t>
-  </si>
-  <si>
-    <t>2026타인10197</t>
-  </si>
-  <si>
-    <t>2026타인2101</t>
-  </si>
-  <si>
-    <t>2026타인10144</t>
-  </si>
-  <si>
-    <t>2026타인100238</t>
-  </si>
-  <si>
-    <t>2026타인10236</t>
-  </si>
-  <si>
-    <t>2026타인10239</t>
-  </si>
-  <si>
-    <t>2026타인10348</t>
-  </si>
-  <si>
-    <t>2026타인10341</t>
-  </si>
-  <si>
-    <t>2026타인10085</t>
-  </si>
-  <si>
-    <t>2026타인10075</t>
-  </si>
-  <si>
-    <t>2026타인10300</t>
-  </si>
-  <si>
-    <t>2026타인10193</t>
-  </si>
-  <si>
-    <t>2026타인10196</t>
-  </si>
-  <si>
-    <t>2026타인2103</t>
-  </si>
-  <si>
-    <t>2026타인10143</t>
-  </si>
-  <si>
-    <t>2026타인100237</t>
-  </si>
-  <si>
-    <t>2026타인10235</t>
-  </si>
-  <si>
-    <t>2026타인10238</t>
-  </si>
-  <si>
-    <t>2026타인10347</t>
-  </si>
-  <si>
-    <t>2026타인10340</t>
-  </si>
-  <si>
-    <t>2026타인10242</t>
-  </si>
-  <si>
-    <t>2026타인10151</t>
-  </si>
-  <si>
-    <t>2026타인10155</t>
-  </si>
-  <si>
-    <t>2026타인10157</t>
-  </si>
-  <si>
-    <t>2026타인10160</t>
-  </si>
-  <si>
-    <t>2026타인10162</t>
-  </si>
-  <si>
     <t>2026타인50875</t>
-  </si>
-  <si>
-    <t>2026타인10340.</t>
-  </si>
-  <si>
-    <t>2026타인10346</t>
-  </si>
-  <si>
-    <t>2026타인10359</t>
-  </si>
-  <si>
-    <t>2026타인10361</t>
-  </si>
-  <si>
-    <t>2026타인10357</t>
-  </si>
-  <si>
-    <t>2026타인10133</t>
-  </si>
-  <si>
-    <t>2026타인10243</t>
-  </si>
-  <si>
-    <t>2026타인10152</t>
-  </si>
-  <si>
-    <t>2026타인10156</t>
-  </si>
-  <si>
-    <t>2026타인10158</t>
-  </si>
-  <si>
-    <t>2026타인10161</t>
-  </si>
-  <si>
-    <t>2026타인10163</t>
-  </si>
-  <si>
-    <t>2026타인10360</t>
-  </si>
-  <si>
-    <t>2026타인10362</t>
   </si>
   <si>
     <t>2026타인4233</t>
@@ -940,14 +712,6 @@
   </si>
   <si>
     <t>2026타인4240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026타인10360</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026타인10342</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1027,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,9 +814,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1372,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC6190E-F6A8-4356-BDE2-6BB4C1AFDCC8}">
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24.125" style="5" bestFit="1" customWidth="1"/>
@@ -1394,47 +1155,47 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>94</v>
+      <c r="A2" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>272</v>
+      <c r="A3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>205</v>
+      <c r="A4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>154</v>
+      <c r="A5" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>88</v>
@@ -1442,11 +1203,11 @@
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="9" t="s">
-        <v>91</v>
+      <c r="A6" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>88</v>
@@ -1454,11 +1215,11 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="9" t="s">
-        <v>91</v>
+      <c r="A7" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>88</v>
@@ -1466,11 +1227,11 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>91</v>
+      <c r="A8" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>88</v>
@@ -1478,11 +1239,11 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>208</v>
+      <c r="A9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>88</v>
@@ -1490,11 +1251,11 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>156</v>
+      <c r="A10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>88</v>
@@ -1503,10 +1264,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>88</v>
@@ -1515,10 +1276,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>88</v>
@@ -1527,10 +1288,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>88</v>
@@ -1539,10 +1300,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>88</v>
@@ -1551,10 +1312,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>88</v>
@@ -1563,10 +1324,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>88</v>
@@ -1575,10 +1336,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>88</v>
@@ -1587,10 +1348,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>88</v>
@@ -1599,10 +1360,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>88</v>
@@ -1611,10 +1372,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>88</v>
@@ -1623,10 +1384,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>88</v>
@@ -1635,10 +1396,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>88</v>
@@ -1647,10 +1408,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>88</v>
@@ -1659,10 +1420,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>88</v>
@@ -1671,10 +1432,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>88</v>
@@ -1683,10 +1444,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>88</v>
@@ -1695,10 +1456,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>88</v>
@@ -1707,10 +1468,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>88</v>
@@ -1719,10 +1480,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>88</v>
@@ -1731,10 +1492,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>88</v>
@@ -1743,10 +1504,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>88</v>
@@ -1755,10 +1516,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>88</v>
@@ -1767,10 +1528,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>168</v>
+        <v>89</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>88</v>
@@ -1779,10 +1540,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>219</v>
+        <v>89</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>88</v>
@@ -1791,10 +1552,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>220</v>
+        <v>89</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>88</v>
@@ -1803,10 +1564,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>169</v>
+        <v>89</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>88</v>
@@ -1815,10 +1576,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>88</v>
@@ -1827,10 +1588,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>88</v>
@@ -1839,10 +1600,10 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>88</v>
@@ -1851,10 +1612,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>88</v>
@@ -1863,10 +1624,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>88</v>
@@ -1875,10 +1636,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>88</v>
@@ -1886,10 +1647,10 @@
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="2" t="s">
+      <c r="A43" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>174</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -1899,10 +1660,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>225</v>
+        <v>89</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>88</v>
@@ -1910,11 +1671,11 @@
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>207</v>
+      <c r="A45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>88</v>
@@ -1923,10 +1684,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>88</v>
@@ -1935,10 +1696,10 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>88</v>
@@ -1947,10 +1708,10 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>88</v>
@@ -1959,10 +1720,10 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>88</v>
@@ -1971,10 +1732,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>88</v>
@@ -1983,10 +1744,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>88</v>
@@ -1995,10 +1756,10 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>228</v>
+        <v>89</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>88</v>
@@ -2007,10 +1768,10 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>88</v>
@@ -2019,10 +1780,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>107</v>
+        <v>89</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>88</v>
@@ -2031,10 +1792,10 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>189</v>
+        <v>89</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>88</v>
@@ -2043,10 +1804,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>229</v>
+        <v>89</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>88</v>
@@ -2055,10 +1816,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>88</v>
@@ -2067,10 +1828,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>88</v>
@@ -2079,10 +1840,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>88</v>
@@ -2091,10 +1852,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>88</v>
@@ -2103,10 +1864,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>88</v>
@@ -2115,10 +1876,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>88</v>
@@ -2127,10 +1888,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>88</v>
@@ -2139,10 +1900,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>88</v>
@@ -2151,10 +1912,10 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>88</v>
@@ -2163,10 +1924,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>88</v>
@@ -2175,10 +1936,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>245</v>
+        <v>89</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>88</v>
@@ -2187,10 +1948,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>88</v>
@@ -2199,10 +1960,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>88</v>
@@ -2211,10 +1972,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>88</v>
@@ -2223,10 +1984,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>88</v>
@@ -2235,10 +1996,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>198</v>
+        <v>89</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>88</v>
@@ -2247,10 +2008,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>88</v>
@@ -2259,10 +2020,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>249</v>
+        <v>89</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>88</v>
@@ -2271,10 +2032,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>88</v>
@@ -2283,10 +2044,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>114</v>
+        <v>89</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>88</v>
@@ -2295,10 +2056,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>88</v>
@@ -2307,10 +2068,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>248</v>
+        <v>89</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>88</v>
@@ -2319,10 +2080,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>196</v>
+        <v>89</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>88</v>
@@ -2331,188 +2092,186 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8">
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8">
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:3">
       <c r="A83" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:3">
       <c r="A84" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:3">
       <c r="A85" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>231</v>
+        <v>89</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:3">
       <c r="A86" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:3">
       <c r="A87" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>111</v>
+        <v>89</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:3">
       <c r="A88" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:3">
       <c r="A89" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:3">
       <c r="A90" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:3">
       <c r="A91" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:3">
       <c r="A92" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:3">
       <c r="A93" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:3">
       <c r="A94" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:3">
       <c r="A95" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:3">
       <c r="A96" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>88</v>
@@ -2520,10 +2279,10 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>88</v>
@@ -2531,10 +2290,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>88</v>
@@ -2542,10 +2301,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>88</v>
@@ -2553,10 +2312,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>88</v>
@@ -2564,10 +2323,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>88</v>
@@ -2575,10 +2334,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>88</v>
@@ -2586,10 +2345,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>239</v>
+        <v>89</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>88</v>
@@ -2597,10 +2356,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>88</v>
@@ -2608,10 +2367,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>88</v>
@@ -2619,10 +2378,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>88</v>
@@ -2630,10 +2389,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>88</v>
@@ -2641,10 +2400,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>88</v>
@@ -2652,10 +2411,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>88</v>
@@ -2663,10 +2422,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>88</v>
@@ -2674,10 +2433,10 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>132</v>
+        <v>89</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>88</v>
@@ -2685,10 +2444,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>88</v>
@@ -2696,10 +2455,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>88</v>
@@ -2707,10 +2466,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>88</v>
@@ -2718,10 +2477,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>251</v>
+        <v>89</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>88</v>
@@ -2729,10 +2488,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>88</v>
@@ -2740,10 +2499,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>134</v>
+        <v>89</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>88</v>
@@ -2751,10 +2510,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>88</v>
@@ -2762,10 +2521,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>252</v>
+        <v>89</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>88</v>
@@ -2773,10 +2532,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>88</v>
@@ -2784,10 +2543,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>88</v>
@@ -2795,10 +2554,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>88</v>
@@ -2806,10 +2565,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>88</v>
@@ -2817,10 +2576,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>139</v>
+        <v>89</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>88</v>
@@ -2828,10 +2587,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>88</v>
@@ -2839,10 +2598,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>253</v>
+        <v>89</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>88</v>
@@ -2850,10 +2609,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>88</v>
@@ -2861,10 +2620,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>88</v>
@@ -2872,10 +2631,10 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>142</v>
+        <v>89</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>88</v>
@@ -2883,10 +2642,10 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>88</v>
@@ -2894,10 +2653,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>88</v>
@@ -2905,10 +2664,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>204</v>
+        <v>89</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>88</v>
@@ -2916,10 +2675,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>88</v>
@@ -2927,10 +2686,10 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>300</v>
+        <v>89</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>88</v>
@@ -2938,10 +2697,10 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>301</v>
+        <v>87</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>88</v>
@@ -2949,32 +2708,32 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>246</v>
+        <v>4</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>268</v>
+      <c r="A137" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>291</v>
+      <c r="A138" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>88</v>
@@ -2982,10 +2741,10 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>273</v>
+        <v>7</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>88</v>
@@ -2993,10 +2752,10 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>261</v>
+        <v>8</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>88</v>
@@ -3004,10 +2763,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>280</v>
+        <v>9</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>88</v>
@@ -3015,10 +2774,10 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>88</v>
@@ -3026,10 +2785,10 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>88</v>
@@ -3037,10 +2796,10 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>281</v>
+        <v>87</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>88</v>
@@ -3048,10 +2807,10 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>294</v>
+        <v>87</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>88</v>
@@ -3059,10 +2818,10 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>282</v>
+        <v>87</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>88</v>
@@ -3070,10 +2829,10 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>295</v>
+        <v>87</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>88</v>
@@ -3081,10 +2840,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>283</v>
+        <v>87</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>88</v>
@@ -3092,10 +2851,10 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>296</v>
+        <v>87</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>88</v>
@@ -3103,10 +2862,10 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>284</v>
+        <v>87</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>88</v>
@@ -3114,10 +2873,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>297</v>
+        <v>91</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>88</v>
@@ -3125,10 +2884,10 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>144</v>
+        <v>91</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>88</v>
@@ -3136,54 +2895,54 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>101</v>
+      <c r="A154" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>102</v>
+      <c r="A155" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>267</v>
+      <c r="A156" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>273</v>
+      <c r="A157" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>88</v>
@@ -3191,10 +2950,10 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>88</v>
@@ -3202,10 +2961,10 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>270</v>
+        <v>87</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>88</v>
@@ -3213,10 +2972,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>258</v>
+        <v>87</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>88</v>
@@ -3224,10 +2983,10 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>88</v>
@@ -3235,10 +2994,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>271</v>
+        <v>87</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>88</v>
@@ -3246,10 +3005,10 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>259</v>
+        <v>87</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>88</v>
@@ -3257,10 +3016,10 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>88</v>
@@ -3268,10 +3027,10 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>88</v>
@@ -3279,10 +3038,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>275</v>
+        <v>36</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>88</v>
@@ -3290,10 +3049,10 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>263</v>
+        <v>87</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>88</v>
@@ -3301,10 +3060,10 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>276</v>
+        <v>87</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>88</v>
@@ -3312,10 +3071,10 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>264</v>
+        <v>87</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>88</v>
@@ -3323,10 +3082,10 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>88</v>
@@ -3334,10 +3093,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>88</v>
@@ -3345,10 +3104,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>279</v>
+        <v>39</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>88</v>
@@ -3356,10 +3115,10 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>292</v>
+        <v>40</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>88</v>
@@ -3367,10 +3126,10 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>274</v>
+        <v>41</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>88</v>
@@ -3378,32 +3137,32 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>262</v>
+        <v>87</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>269</v>
+      <c r="A176" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>257</v>
+      <c r="A177" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>88</v>
@@ -3411,10 +3170,10 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>88</v>
@@ -3422,10 +3181,10 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C179" s="7" t="s">
         <v>88</v>
@@ -3433,10 +3192,10 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>278</v>
+        <v>47</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>88</v>
@@ -3444,10 +3203,10 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>266</v>
+        <v>48</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>88</v>
@@ -3455,10 +3214,10 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>303</v>
+        <v>87</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>88</v>
@@ -3466,10 +3225,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>88</v>
@@ -3477,10 +3236,10 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>88</v>
@@ -3488,10 +3247,10 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>123</v>
+        <v>87</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>88</v>
@@ -3499,10 +3258,10 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>88</v>
@@ -3510,10 +3269,10 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>88</v>
@@ -3521,10 +3280,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>88</v>
@@ -3532,10 +3291,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>88</v>
@@ -3543,10 +3302,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>88</v>
@@ -3554,10 +3313,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>88</v>
@@ -3565,10 +3324,10 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>88</v>
@@ -3576,10 +3335,10 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>148</v>
+        <v>87</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C193" s="7" t="s">
         <v>88</v>
@@ -3587,10 +3346,10 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>288</v>
+        <v>61</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>88</v>
@@ -3598,10 +3357,10 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>298</v>
+        <v>62</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>88</v>
@@ -3609,10 +3368,10 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="C196" s="7" t="s">
         <v>88</v>
@@ -3620,10 +3379,10 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>299</v>
+        <v>87</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>88</v>
@@ -3634,7 +3393,7 @@
         <v>87</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>88</v>
@@ -3644,8 +3403,8 @@
       <c r="A199" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B199" s="5" t="s">
-        <v>4</v>
+      <c r="B199" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C199" s="7" t="s">
         <v>88</v>
@@ -3656,7 +3415,7 @@
         <v>87</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>88</v>
@@ -3667,7 +3426,7 @@
         <v>87</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>88</v>
@@ -3677,8 +3436,8 @@
       <c r="A202" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B202" s="4" t="s">
-        <v>7</v>
+      <c r="B202" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>88</v>
@@ -3688,8 +3447,8 @@
       <c r="A203" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B203" s="5" t="s">
-        <v>8</v>
+      <c r="B203" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C203" s="7" t="s">
         <v>88</v>
@@ -3700,7 +3459,7 @@
         <v>87</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="C204" s="7" t="s">
         <v>88</v>
@@ -3711,7 +3470,7 @@
         <v>87</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>88</v>
@@ -3722,7 +3481,7 @@
         <v>87</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>88</v>
@@ -3732,8 +3491,8 @@
       <c r="A207" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B207" s="5" t="s">
-        <v>11</v>
+      <c r="B207" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>88</v>
@@ -3744,7 +3503,7 @@
         <v>87</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>88</v>
@@ -3754,8 +3513,8 @@
       <c r="A209" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B209" s="5" t="s">
-        <v>13</v>
+      <c r="B209" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>88</v>
@@ -3766,7 +3525,7 @@
         <v>87</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>88</v>
@@ -3777,7 +3536,7 @@
         <v>87</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>88</v>
@@ -3788,7 +3547,7 @@
         <v>87</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>88</v>
@@ -3799,7 +3558,7 @@
         <v>87</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="C213" s="7" t="s">
         <v>88</v>
@@ -3807,10 +3566,10 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>88</v>
@@ -3818,10 +3577,10 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>88</v>
@@ -3832,7 +3591,7 @@
         <v>87</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>88</v>
@@ -3842,8 +3601,8 @@
       <c r="A217" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B217" s="4" t="s">
-        <v>21</v>
+      <c r="B217" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>88</v>
@@ -3854,7 +3613,7 @@
         <v>87</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>88</v>
@@ -3864,960 +3623,288 @@
       <c r="A219" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B219" s="4" t="s">
-        <v>23</v>
+      <c r="B219" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="B220" s="3"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A221" s="3"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C222" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="B222" s="3"/>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C223" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A223" s="3"/>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C224" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
-      <c r="A225" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C225" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C226" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C228" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C229" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C230" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C231" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B232" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C232" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C233" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B234" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C235" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B236" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C236" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C237" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B238" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C238" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C239" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C241" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C242" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C243" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B244" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C244" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C245" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B246" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C246" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B247" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C247" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C248" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B249" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C249" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B250" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C250" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B251" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C251" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B252" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C253" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B254" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C254" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B256" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B257" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C258" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B259" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C259" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B260" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C260" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3">
-      <c r="A261" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B261" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C261" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="A262" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B262" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C262" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3">
-      <c r="A263" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C263" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3">
-      <c r="A264" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B264" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C264" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="A265" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C265" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B266" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C266" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C267" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3">
-      <c r="A268" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C268" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3">
-      <c r="A269" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B269" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C269" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B270" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C270" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B271" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C271" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B272" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C272" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3">
-      <c r="A273" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B273" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C273" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3">
-      <c r="A274" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C274" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B275" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C275" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C276" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C277" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B278" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C278" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3">
-      <c r="A279" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C279" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B280" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C280" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C281" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
-      <c r="A282" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B282" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C282" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C283" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B284" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C284" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3">
-      <c r="A285" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C285" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B286" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C286" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="A287" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B288" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C288" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C289" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B290" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C290" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B291" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C291" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B292" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C292" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B293" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C293" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B294" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B295" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C295" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C296" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="A297" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B297" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="C297" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3">
-      <c r="A298" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B298" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="C298" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C299" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B300" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C300" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C301" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
-      <c r="A302" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B302" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C302" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3">
-      <c r="A303" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B303" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C303" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="B304" s="3"/>
+      <c r="B224" s="2"/>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2"/>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="B226" s="4"/>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="B227" s="4"/>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="B228" s="4"/>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="B229" s="4"/>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="B230" s="4"/>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="B231" s="4"/>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="4"/>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="B233" s="4"/>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="B234" s="4"/>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="B235" s="4"/>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="B236" s="4"/>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="B237" s="4"/>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="4"/>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="B239" s="4"/>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="B240" s="4"/>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="B241" s="4"/>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="4"/>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="B243" s="4"/>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="B244" s="4"/>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="B245" s="4"/>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="B246" s="4"/>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="B247" s="4"/>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="4"/>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="B249" s="4"/>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="4"/>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="B251" s="4"/>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="B252" s="4"/>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="B253" s="4"/>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="B254" s="4"/>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="B255" s="4"/>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="4"/>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="B257" s="4"/>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="B258" s="4"/>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="B259" s="4"/>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="4"/>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="B261" s="4"/>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="B262" s="4"/>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="4"/>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="B264" s="4"/>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="B265" s="4"/>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="B266" s="4"/>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="B267" s="4"/>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="B268" s="4"/>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="B269" s="4"/>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="B270" s="4"/>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="B271" s="4"/>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="B272" s="4"/>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="B273" s="4"/>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="4"/>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="B275" s="4"/>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="B276" s="4"/>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="B277" s="4"/>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="B278" s="4"/>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="4"/>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="B280" s="4"/>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="B281" s="4"/>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="B282" s="4"/>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="B283" s="4"/>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="4"/>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="B285" s="4"/>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="B286" s="4"/>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="4"/>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="B288" s="4"/>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="4"/>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="B290" s="4"/>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="B291" s="4"/>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="B292" s="4"/>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="B293" s="4"/>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="B294" s="4"/>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="B295" s="4"/>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="B296" s="4"/>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="4"/>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="B298" s="4"/>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="B299" s="4"/>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="B300" s="4"/>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="4"/>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="B302" s="4"/>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="4"/>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="B304" s="4"/>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="3"/>
+      <c r="B305" s="4"/>
     </row>
     <row r="306" spans="1:2">
-      <c r="B306" s="3"/>
+      <c r="A306" s="4"/>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="3"/>
+      <c r="B307" s="4"/>
     </row>
     <row r="308" spans="1:2">
-      <c r="B308" s="2"/>
+      <c r="B308" s="4"/>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="2"/>
+      <c r="A309" s="4"/>
     </row>
     <row r="310" spans="1:2">
       <c r="B310" s="4"/>
     </row>
     <row r="311" spans="1:2">
-      <c r="B311" s="4"/>
+      <c r="A311" s="4"/>
     </row>
     <row r="312" spans="1:2">
       <c r="B312" s="4"/>
@@ -4832,13 +3919,13 @@
       <c r="B315" s="4"/>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="4"/>
+      <c r="B316" s="4"/>
     </row>
     <row r="317" spans="1:2">
       <c r="B317" s="4"/>
     </row>
     <row r="318" spans="1:2">
-      <c r="B318" s="4"/>
+      <c r="A318" s="4"/>
     </row>
     <row r="319" spans="1:2">
       <c r="B319" s="4"/>
@@ -4847,10 +3934,10 @@
       <c r="B320" s="4"/>
     </row>
     <row r="321" spans="1:2">
-      <c r="B321" s="4"/>
+      <c r="A321" s="4"/>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="4"/>
+      <c r="B322" s="4"/>
     </row>
     <row r="323" spans="1:2">
       <c r="B323" s="4"/>
@@ -4862,70 +3949,70 @@
       <c r="B325" s="4"/>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="4"/>
+      <c r="B326" s="4"/>
     </row>
     <row r="327" spans="1:2">
-      <c r="B327" s="4"/>
+      <c r="A327" s="4"/>
     </row>
     <row r="328" spans="1:2">
       <c r="B328" s="4"/>
     </row>
     <row r="329" spans="1:2">
-      <c r="B329" s="4"/>
+      <c r="A329" s="4"/>
     </row>
     <row r="330" spans="1:2">
       <c r="B330" s="4"/>
     </row>
     <row r="331" spans="1:2">
-      <c r="B331" s="4"/>
+      <c r="A331" s="4"/>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="4"/>
+      <c r="B332" s="4"/>
     </row>
     <row r="333" spans="1:2">
-      <c r="B333" s="4"/>
+      <c r="A333" s="4"/>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="4"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="335" spans="1:2">
-      <c r="B335" s="4"/>
+      <c r="A335" s="4"/>
     </row>
     <row r="336" spans="1:2">
-      <c r="B336" s="4"/>
+      <c r="B336" s="3"/>
     </row>
     <row r="337" spans="1:2">
-      <c r="B337" s="4"/>
+      <c r="B337" s="3"/>
     </row>
     <row r="338" spans="1:2">
-      <c r="B338" s="4"/>
+      <c r="A338" s="3"/>
     </row>
     <row r="339" spans="1:2">
-      <c r="B339" s="4"/>
+      <c r="A339" s="3"/>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="4"/>
+      <c r="B340" s="4"/>
     </row>
     <row r="341" spans="1:2">
-      <c r="B341" s="4"/>
+      <c r="A341" s="4"/>
     </row>
     <row r="342" spans="1:2">
       <c r="B342" s="4"/>
     </row>
     <row r="343" spans="1:2">
-      <c r="B343" s="4"/>
+      <c r="A343" s="4"/>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="4"/>
+      <c r="B344" s="4"/>
     </row>
     <row r="345" spans="1:2">
       <c r="B345" s="4"/>
     </row>
     <row r="346" spans="1:2">
-      <c r="B346" s="4"/>
+      <c r="A346" s="4"/>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="4"/>
+      <c r="B347" s="4"/>
     </row>
     <row r="348" spans="1:2">
       <c r="B348" s="4"/>
@@ -4937,296 +4024,44 @@
       <c r="B350" s="4"/>
     </row>
     <row r="351" spans="1:2">
-      <c r="B351" s="4"/>
+      <c r="A351" s="4"/>
     </row>
     <row r="352" spans="1:2">
       <c r="B352" s="4"/>
     </row>
     <row r="353" spans="1:2">
-      <c r="B353" s="4"/>
+      <c r="A353" s="4"/>
     </row>
     <row r="354" spans="1:2">
       <c r="B354" s="4"/>
     </row>
     <row r="355" spans="1:2">
-      <c r="B355" s="4"/>
+      <c r="A355" s="4"/>
     </row>
     <row r="356" spans="1:2">
       <c r="B356" s="4"/>
     </row>
     <row r="357" spans="1:2">
-      <c r="B357" s="4"/>
+      <c r="A357" s="4"/>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="4"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="359" spans="1:2">
       <c r="B359" s="4"/>
     </row>
     <row r="360" spans="1:2">
+      <c r="A360" s="6"/>
       <c r="B360" s="4"/>
     </row>
-    <row r="361" spans="1:2">
-      <c r="B361" s="4"/>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="B362" s="4"/>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" s="4"/>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="B364" s="4"/>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="B365" s="4"/>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="B366" s="4"/>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="B367" s="4"/>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" s="4"/>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="B369" s="4"/>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="B370" s="4"/>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" s="4"/>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="B372" s="4"/>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" s="4"/>
-    </row>
-    <row r="374" spans="1:2">
-      <c r="B374" s="4"/>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="B375" s="4"/>
-    </row>
-    <row r="376" spans="1:2">
-      <c r="B376" s="4"/>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="B377" s="4"/>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="B378" s="4"/>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="B379" s="4"/>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="B380" s="4"/>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" s="4"/>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="B382" s="4"/>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="B383" s="4"/>
-    </row>
-    <row r="384" spans="1:2">
-      <c r="B384" s="4"/>
-    </row>
-    <row r="385" spans="1:2">
-      <c r="A385" s="4"/>
-    </row>
-    <row r="386" spans="1:2">
-      <c r="B386" s="4"/>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" s="4"/>
-    </row>
-    <row r="388" spans="1:2">
-      <c r="B388" s="4"/>
-    </row>
-    <row r="389" spans="1:2">
-      <c r="B389" s="4"/>
-    </row>
-    <row r="390" spans="1:2">
-      <c r="A390" s="4"/>
-    </row>
-    <row r="391" spans="1:2">
-      <c r="B391" s="4"/>
-    </row>
-    <row r="392" spans="1:2">
-      <c r="B392" s="4"/>
-    </row>
-    <row r="393" spans="1:2">
-      <c r="A393" s="4"/>
-    </row>
-    <row r="394" spans="1:2">
-      <c r="B394" s="4"/>
-    </row>
-    <row r="395" spans="1:2">
-      <c r="A395" s="4"/>
-    </row>
-    <row r="396" spans="1:2">
-      <c r="B396" s="4"/>
-    </row>
-    <row r="397" spans="1:2">
-      <c r="B397" s="4"/>
-    </row>
-    <row r="398" spans="1:2">
-      <c r="B398" s="4"/>
-    </row>
-    <row r="399" spans="1:2">
-      <c r="B399" s="4"/>
-    </row>
-    <row r="400" spans="1:2">
-      <c r="B400" s="4"/>
-    </row>
-    <row r="401" spans="1:2">
-      <c r="B401" s="4"/>
-    </row>
-    <row r="402" spans="1:2">
-      <c r="A402" s="4"/>
-    </row>
-    <row r="403" spans="1:2">
-      <c r="B403" s="4"/>
-    </row>
-    <row r="404" spans="1:2">
-      <c r="B404" s="4"/>
-    </row>
-    <row r="405" spans="1:2">
-      <c r="A405" s="4"/>
-    </row>
-    <row r="406" spans="1:2">
-      <c r="B406" s="4"/>
-    </row>
-    <row r="407" spans="1:2">
-      <c r="B407" s="4"/>
-    </row>
-    <row r="408" spans="1:2">
-      <c r="B408" s="4"/>
-    </row>
-    <row r="409" spans="1:2">
-      <c r="B409" s="4"/>
-    </row>
-    <row r="410" spans="1:2">
-      <c r="B410" s="4"/>
-    </row>
-    <row r="411" spans="1:2">
-      <c r="A411" s="4"/>
-    </row>
-    <row r="412" spans="1:2">
-      <c r="B412" s="4"/>
-    </row>
-    <row r="413" spans="1:2">
-      <c r="A413" s="4"/>
-    </row>
-    <row r="414" spans="1:2">
-      <c r="B414" s="4"/>
-    </row>
-    <row r="415" spans="1:2">
-      <c r="A415" s="4"/>
-    </row>
-    <row r="416" spans="1:2">
-      <c r="B416" s="4"/>
-    </row>
-    <row r="417" spans="1:2">
-      <c r="A417" s="4"/>
-    </row>
-    <row r="418" spans="1:2">
-      <c r="B418" s="4"/>
-    </row>
-    <row r="419" spans="1:2">
-      <c r="A419" s="4"/>
-    </row>
-    <row r="420" spans="1:2">
-      <c r="B420" s="3"/>
-    </row>
-    <row r="421" spans="1:2">
-      <c r="B421" s="3"/>
-    </row>
-    <row r="422" spans="1:2">
-      <c r="A422" s="3"/>
-    </row>
-    <row r="423" spans="1:2">
-      <c r="A423" s="3"/>
-    </row>
-    <row r="424" spans="1:2">
-      <c r="B424" s="4"/>
-    </row>
-    <row r="425" spans="1:2">
-      <c r="A425" s="4"/>
-    </row>
-    <row r="426" spans="1:2">
-      <c r="B426" s="4"/>
-    </row>
-    <row r="427" spans="1:2">
-      <c r="A427" s="4"/>
-    </row>
-    <row r="428" spans="1:2">
-      <c r="B428" s="4"/>
-    </row>
-    <row r="429" spans="1:2">
-      <c r="B429" s="4"/>
-    </row>
-    <row r="430" spans="1:2">
-      <c r="A430" s="4"/>
-    </row>
-    <row r="431" spans="1:2">
-      <c r="B431" s="4"/>
-    </row>
-    <row r="432" spans="1:2">
-      <c r="B432" s="4"/>
-    </row>
-    <row r="433" spans="1:2">
-      <c r="B433" s="4"/>
-    </row>
-    <row r="434" spans="1:2">
-      <c r="B434" s="4"/>
-    </row>
-    <row r="435" spans="1:2">
-      <c r="A435" s="4"/>
-    </row>
-    <row r="436" spans="1:2">
-      <c r="B436" s="4"/>
-    </row>
-    <row r="437" spans="1:2">
-      <c r="A437" s="4"/>
-    </row>
-    <row r="438" spans="1:2">
-      <c r="B438" s="4"/>
-    </row>
-    <row r="439" spans="1:2">
-      <c r="A439" s="4"/>
-    </row>
-    <row r="440" spans="1:2">
-      <c r="B440" s="4"/>
-    </row>
-    <row r="441" spans="1:2">
-      <c r="A441" s="4"/>
-    </row>
-    <row r="442" spans="1:2">
-      <c r="B442" s="4"/>
-    </row>
-    <row r="443" spans="1:2">
-      <c r="B443" s="4"/>
-    </row>
-    <row r="444" spans="1:2">
-      <c r="A444" s="6"/>
-      <c r="B444" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C444" xr:uid="{C9EB9D7D-12FD-4816-92B0-7F8FD3F3875E}">
-    <sortState ref="A2:C402">
+  <autoFilter ref="A1:C360" xr:uid="{C9EB9D7D-12FD-4816-92B0-7F8FD3F3875E}">
+    <sortState ref="A2:C318">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:C303">
-    <sortCondition ref="A5"/>
+  <sortState ref="A2:C219">
+    <sortCondition ref="A3"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\전재룡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F30E864-BB62-454E-AE57-1B84B9FCCC4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759543BF-FE27-4493-AE11-617ABC61A71D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="10065" xr2:uid="{8D0F9930-D084-4684-8A7C-5888118A9192}"/>
   </bookViews>
   <sheets>
-    <sheet name="인천남부법원" sheetId="1" r:id="rId1"/>
+    <sheet name="전체" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">인천남부법원!$A$1:$C$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">전체!$A$1:$C$360</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="198">
   <si>
     <t>법원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -41,46 +41,25 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026타인50848</t>
-  </si>
-  <si>
     <t>2026타인50849</t>
   </si>
   <si>
-    <t>2026타인50855</t>
-  </si>
-  <si>
     <t>2026타인50856</t>
   </si>
   <si>
-    <t>2026타인50862</t>
-  </si>
-  <si>
     <t>2026타인50863</t>
   </si>
   <si>
-    <t>2026타인50866</t>
-  </si>
-  <si>
     <t>2026타인50867</t>
   </si>
   <si>
     <t>2026타인50876</t>
   </si>
   <si>
-    <t>2026타인50877</t>
-  </si>
-  <si>
     <t>2026타인50878</t>
   </si>
   <si>
-    <t>2026타인50883</t>
-  </si>
-  <si>
     <t>2026타인50884</t>
-  </si>
-  <si>
-    <t>2026타인50887</t>
   </si>
   <si>
     <t>2026타인50888</t>
@@ -311,39 +290,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2026타인4113</t>
-  </si>
-  <si>
-    <t>2026타인4134</t>
-  </si>
-  <si>
-    <t>2026타인4154</t>
-  </si>
-  <si>
-    <t>2026타인4159</t>
-  </si>
-  <si>
-    <t>2026타인4161</t>
-  </si>
-  <si>
-    <t>2026타인4175</t>
-  </si>
-  <si>
-    <t>2026타인4173</t>
-  </si>
-  <si>
-    <t>2026타인4171</t>
-  </si>
-  <si>
-    <t>2026타인4162</t>
-  </si>
-  <si>
-    <t>2026타인4156</t>
-  </si>
-  <si>
-    <t>2026타인4153</t>
-  </si>
-  <si>
     <t>2026타인4197</t>
   </si>
   <si>
@@ -398,141 +344,9 @@
     <t>2026타인4225</t>
   </si>
   <si>
-    <t>2026타인3783</t>
-  </si>
-  <si>
-    <t>2026타인3784</t>
-  </si>
-  <si>
-    <t>2026타인3939</t>
-  </si>
-  <si>
-    <t>2026타인3928</t>
-  </si>
-  <si>
-    <t>2026타인3966</t>
-  </si>
-  <si>
-    <t>2026타인3968</t>
-  </si>
-  <si>
-    <t>2026타인3975</t>
-  </si>
-  <si>
-    <t>2026타인3989</t>
-  </si>
-  <si>
-    <t>2026타인3996</t>
-  </si>
-  <si>
-    <t>2026타인4000</t>
-  </si>
-  <si>
-    <t>2026타인4004</t>
-  </si>
-  <si>
-    <t>2026타인4007</t>
-  </si>
-  <si>
-    <t>2026타인4017</t>
-  </si>
-  <si>
-    <t>2026타인4032</t>
-  </si>
-  <si>
-    <t>2026타인4035</t>
-  </si>
-  <si>
-    <t>2026타인4053</t>
-  </si>
-  <si>
-    <t>2026타인4060</t>
-  </si>
-  <si>
-    <t>2026타인4026</t>
-  </si>
-  <si>
-    <t>2026타인4069</t>
-  </si>
-  <si>
-    <t>2026타인4089</t>
-  </si>
-  <si>
-    <t>2026타인4091</t>
-  </si>
-  <si>
-    <t>2026타인4118</t>
-  </si>
-  <si>
-    <t>2026타인4123</t>
-  </si>
-  <si>
-    <t>2026타인4127</t>
-  </si>
-  <si>
-    <t>2026타인4133</t>
-  </si>
-  <si>
-    <t>2026타인4167</t>
-  </si>
-  <si>
-    <t>2026타인4169</t>
-  </si>
-  <si>
-    <t>2026타인4176</t>
-  </si>
-  <si>
-    <t>2026타인4179</t>
-  </si>
-  <si>
-    <t>2026타인4182</t>
-  </si>
-  <si>
-    <t>2026타인4184</t>
-  </si>
-  <si>
-    <t>2026타인4186</t>
-  </si>
-  <si>
-    <t>2026타인4188</t>
-  </si>
-  <si>
-    <t>2026타인4190</t>
-  </si>
-  <si>
-    <t>2026타인4192</t>
-  </si>
-  <si>
     <t>2026타인4135</t>
   </si>
   <si>
-    <t>2026타인4139</t>
-  </si>
-  <si>
-    <t>2026타인4141</t>
-  </si>
-  <si>
-    <t>2026타인4144</t>
-  </si>
-  <si>
-    <t>2026타인4149</t>
-  </si>
-  <si>
-    <t>2026타인4151</t>
-  </si>
-  <si>
-    <t>2026타인4155</t>
-  </si>
-  <si>
-    <t>2026타인4166</t>
-  </si>
-  <si>
-    <t>2026타인4164</t>
-  </si>
-  <si>
-    <t>2026타인4158</t>
-  </si>
-  <si>
     <t>2026타인4206</t>
   </si>
   <si>
@@ -542,9 +356,6 @@
     <t>2026타인4212</t>
   </si>
   <si>
-    <t>2026타인4219</t>
-  </si>
-  <si>
     <t>2026타인4227</t>
   </si>
   <si>
@@ -554,15 +365,9 @@
     <t>2026타인3782</t>
   </si>
   <si>
-    <t>2026타인3785</t>
-  </si>
-  <si>
     <t>2026타인4100</t>
   </si>
   <si>
-    <t>2026타인3931</t>
-  </si>
-  <si>
     <t>2026타인3967</t>
   </si>
   <si>
@@ -704,14 +509,125 @@
     <t>2026타인4230</t>
   </si>
   <si>
-    <t>2026타인50875</t>
+    <t>서울중앙지방법원</t>
+  </si>
+  <si>
+    <t>2026타인10007</t>
+  </si>
+  <si>
+    <t>2026타인10046</t>
+  </si>
+  <si>
+    <t>인천지방법원 부천지원</t>
+  </si>
+  <si>
+    <t>2026타인10330</t>
+  </si>
+  <si>
+    <t>2026타인10194</t>
+  </si>
+  <si>
+    <t>2026타인10197</t>
+  </si>
+  <si>
+    <t>서울서부지방법원</t>
+  </si>
+  <si>
+    <t>2026타인5044</t>
+  </si>
+  <si>
+    <t>서울북부지방법원</t>
+  </si>
+  <si>
+    <t>2026타인10144</t>
+  </si>
+  <si>
+    <t>수원지방법원</t>
+  </si>
+  <si>
+    <t>2026타인100238</t>
+  </si>
+  <si>
+    <t>2026타인10236</t>
+  </si>
+  <si>
+    <t>2026타인10238</t>
+  </si>
+  <si>
+    <t>의정부지방법원 고양지원</t>
+  </si>
+  <si>
+    <t>2026타인10338</t>
+  </si>
+  <si>
+    <t>2026타인10348</t>
+  </si>
+  <si>
+    <t>2026타인10341</t>
+  </si>
+  <si>
+    <t>2026타인10241</t>
+  </si>
+  <si>
+    <t>2026타인10242</t>
+  </si>
+  <si>
+    <t>2026타인10152</t>
+  </si>
+  <si>
+    <t>2026타인10156</t>
+  </si>
+  <si>
+    <t>2026타인10158</t>
+  </si>
+  <si>
+    <t>2026타인10163</t>
+  </si>
+  <si>
+    <t>2026타인10343</t>
+  </si>
+  <si>
+    <t>2026타인10347</t>
+  </si>
+  <si>
+    <t>2026타인10360</t>
+  </si>
+  <si>
+    <t>2026타인10361</t>
+  </si>
+  <si>
+    <t>2026타인10356</t>
+  </si>
+  <si>
+    <t>2026타인10358</t>
+  </si>
+  <si>
+    <t>2026타인10359</t>
+  </si>
+  <si>
+    <t>2026타인10363</t>
+  </si>
+  <si>
+    <t>2026타인10364</t>
+  </si>
+  <si>
+    <t>2026타인10365</t>
+  </si>
+  <si>
+    <t>2026타인10239</t>
+  </si>
+  <si>
+    <t>2026타인10243</t>
+  </si>
+  <si>
+    <t>2026타인10362</t>
+  </si>
+  <si>
+    <t>2026타인10360</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>2026타인4233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026타인4240</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -791,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -817,6 +733,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1156,2479 +1075,2283 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>172</v>
+        <v>82</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>121</v>
+      <c r="A3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>122</v>
+      <c r="A4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>173</v>
+      <c r="A5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>124</v>
+      <c r="A6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>175</v>
+      <c r="A7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>123</v>
+      <c r="A8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>176</v>
+        <v>82</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>177</v>
+        <v>82</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>178</v>
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>179</v>
+        <v>82</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>180</v>
+        <v>82</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>181</v>
+      <c r="A20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>131</v>
+        <v>82</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>182</v>
+        <v>82</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>132</v>
+        <v>82</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>183</v>
+        <v>82</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>133</v>
+        <v>82</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>184</v>
+        <v>82</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>138</v>
+        <v>82</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>189</v>
+        <v>82</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>134</v>
+        <v>82</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>185</v>
+        <v>82</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>82</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>186</v>
+        <v>82</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>187</v>
+        <v>82</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>136</v>
+        <v>82</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>137</v>
+        <v>82</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>188</v>
+        <v>82</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>139</v>
+        <v>82</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>190</v>
+        <v>82</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>140</v>
+        <v>82</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>191</v>
+        <v>82</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>141</v>
+        <v>82</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>192</v>
+        <v>82</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>174</v>
+      <c r="A43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>193</v>
+        <v>82</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>194</v>
+        <v>82</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="C49" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>195</v>
+        <v>82</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>196</v>
+        <v>82</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>207</v>
+        <v>83</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>208</v>
+        <v>82</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>209</v>
+        <v>82</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>210</v>
+        <v>82</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>211</v>
+        <v>82</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>212</v>
+        <v>82</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>216</v>
+        <v>82</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>215</v>
+        <v>167</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>197</v>
+        <v>167</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>214</v>
+        <v>165</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>99</v>
+      <c r="A82" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>198</v>
+      <c r="A83" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>98</v>
+        <v>158</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>97</v>
+        <v>158</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="4" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>199</v>
+        <v>158</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="4" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>200</v>
+        <v>158</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="4" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>201</v>
+        <v>158</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="4" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>202</v>
+        <v>173</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="4" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>203</v>
+        <v>173</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="4" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>204</v>
+        <v>173</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="4" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>205</v>
+        <v>80</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>206</v>
+        <v>80</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>217</v>
+        <v>80</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>218</v>
+        <v>80</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>219</v>
+        <v>80</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>220</v>
+        <v>80</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>221</v>
+        <v>80</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>222</v>
+        <v>80</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>224</v>
+        <v>80</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>225</v>
+        <v>80</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>213</v>
+        <v>80</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>4</v>
+        <v>80</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>8</v>
+        <v>80</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>11</v>
+        <v>80</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>13</v>
+        <v>80</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>17</v>
+        <v>80</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>19</v>
+        <v>80</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>26</v>
+        <v>80</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>31</v>
+        <v>80</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>35</v>
+        <v>80</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>38</v>
+        <v>80</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>40</v>
+        <v>80</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>43</v>
+      <c r="A176" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>48</v>
+        <v>161</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>52</v>
+        <v>161</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>54</v>
+        <v>161</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="4" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="7"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A190" s="4"/>
+      <c r="C190" s="7"/>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="7"/>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A192" s="4"/>
+      <c r="B192" s="4"/>
+      <c r="C192" s="7"/>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A193" s="4"/>
+      <c r="C193" s="7"/>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A194" s="4"/>
+      <c r="B194" s="4"/>
+      <c r="C194" s="7"/>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A195" s="4"/>
+      <c r="C195" s="7"/>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A196" s="4"/>
+      <c r="B196" s="4"/>
+      <c r="C196" s="7"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A197" s="4"/>
+      <c r="B197" s="4"/>
+      <c r="C197" s="7"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A198" s="4"/>
+      <c r="B198" s="4"/>
+      <c r="C198" s="7"/>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A199" s="4"/>
+      <c r="B199" s="4"/>
+      <c r="C199" s="7"/>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A200" s="4"/>
+      <c r="B200" s="4"/>
+      <c r="C200" s="7"/>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A201" s="4"/>
+      <c r="B201" s="4"/>
+      <c r="C201" s="7"/>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A202" s="4"/>
+      <c r="C202" s="7"/>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A203" s="4"/>
+      <c r="B203" s="4"/>
+      <c r="C203" s="7"/>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C204" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A204" s="4"/>
+      <c r="B204" s="4"/>
+      <c r="C204" s="7"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A205" s="4"/>
+      <c r="C205" s="7"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A206" s="4"/>
+      <c r="B206" s="4"/>
+      <c r="C206" s="7"/>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A207" s="4"/>
+      <c r="B207" s="4"/>
+      <c r="C207" s="7"/>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
+      <c r="C208" s="7"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A209" s="4"/>
+      <c r="B209" s="4"/>
+      <c r="C209" s="7"/>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A210" s="4"/>
+      <c r="B210" s="4"/>
+      <c r="C210" s="7"/>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A211" s="4"/>
+      <c r="C211" s="7"/>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B212" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C212" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A212" s="4"/>
+      <c r="B212" s="4"/>
+      <c r="C212" s="7"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A213" s="4"/>
+      <c r="C213" s="7"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A214" s="4"/>
+      <c r="B214" s="4"/>
+      <c r="C214" s="7"/>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A215" s="4"/>
+      <c r="C215" s="7"/>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C216" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A216" s="4"/>
+      <c r="B216" s="4"/>
+      <c r="C216" s="7"/>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C217" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A217" s="4"/>
+      <c r="C217" s="7"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A218" s="4"/>
+      <c r="B218" s="4"/>
+      <c r="C218" s="7"/>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>88</v>
-      </c>
+      <c r="A219" s="4"/>
+      <c r="C219" s="7"/>
     </row>
     <row r="220" spans="1:3">
       <c r="B220" s="3"/>
@@ -4060,8 +3783,8 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:C219">
-    <sortCondition ref="A3"/>
+  <sortState ref="A2:C188">
+    <sortCondition ref="A107"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/court-search/input.xlsx
+++ b/court-search/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\전재룡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780888B3-B288-40B8-9595-75D356DF5D8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84DF4EC3-4494-43AF-923C-C88BD5203D2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="10065" xr2:uid="{8D0F9930-D084-4684-8A7C-5888118A9192}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="67">
   <si>
     <t>법원</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -41,155 +41,197 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>서울남부지방법원</t>
+  </si>
+  <si>
+    <t>의정부지방법원 고양지원</t>
+  </si>
+  <si>
+    <t>서울중앙지방법원</t>
+  </si>
+  <si>
+    <t>수원지방법원</t>
+  </si>
+  <si>
+    <t>인천지방법원 부천지원</t>
+  </si>
+  <si>
     <t>주택</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>서울남부지방법원</t>
-  </si>
-  <si>
-    <t>2026타인4253</t>
-  </si>
-  <si>
-    <t>2026타인4256</t>
-  </si>
-  <si>
-    <t>2026타인4259</t>
-  </si>
-  <si>
-    <t>2026타인4262</t>
-  </si>
-  <si>
-    <t>2026타인4263</t>
-  </si>
-  <si>
-    <t>2026타인4266</t>
-  </si>
-  <si>
-    <t>2026타인4267</t>
-  </si>
-  <si>
-    <t>2026타인4268</t>
-  </si>
-  <si>
-    <t>2026타인4269</t>
-  </si>
-  <si>
-    <t>2026타인4270</t>
-  </si>
-  <si>
-    <t>2026타인4273</t>
-  </si>
-  <si>
-    <t>2026타인4274</t>
-  </si>
-  <si>
-    <t>2026타인4275</t>
-  </si>
-  <si>
-    <t>2026타인4278</t>
-  </si>
-  <si>
-    <t>2026타인4279</t>
-  </si>
-  <si>
-    <t>2026타인4284</t>
-  </si>
-  <si>
-    <t>2026타인4287</t>
-  </si>
-  <si>
-    <t>2026타인4290</t>
-  </si>
-  <si>
-    <t>2026타인4291</t>
-  </si>
-  <si>
-    <t>2026타인4292</t>
-  </si>
-  <si>
-    <t>2026타인4254</t>
-  </si>
-  <si>
-    <t>2026타인5064</t>
-  </si>
-  <si>
-    <t>2026타인4257</t>
-  </si>
-  <si>
-    <t>2026타인4260</t>
-  </si>
-  <si>
-    <t>2026타인4264</t>
-  </si>
-  <si>
-    <t>2026타인4271</t>
-  </si>
-  <si>
-    <t>2026타인4276</t>
-  </si>
-  <si>
-    <t>2026타인4280</t>
-  </si>
-  <si>
-    <t>2026타인5066</t>
-  </si>
-  <si>
-    <t>2026타인4282</t>
-  </si>
-  <si>
-    <t>2026타인4285</t>
-  </si>
-  <si>
-    <t>2026타인4288</t>
-  </si>
-  <si>
-    <t>2026타인4255</t>
-  </si>
-  <si>
-    <t>2026타인5065</t>
-  </si>
-  <si>
-    <t>2026타인4258</t>
-  </si>
-  <si>
-    <t>2026타인4261</t>
-  </si>
-  <si>
-    <t>2026타인4265</t>
-  </si>
-  <si>
-    <t>2026타인4272</t>
-  </si>
-  <si>
-    <t>2026타인4277</t>
-  </si>
-  <si>
-    <t>2026타인4281</t>
-  </si>
-  <si>
-    <t>2026타인5067</t>
-  </si>
-  <si>
-    <t>2026타인4283</t>
-  </si>
-  <si>
-    <t>2026타인4286</t>
-  </si>
-  <si>
-    <t>2026타인4289</t>
-  </si>
-  <si>
-    <t>서울중앙지방법원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>서울서부지방법원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026타인10254</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>2026타인4294</t>
+  </si>
+  <si>
+    <t>2026타인4295</t>
+  </si>
+  <si>
+    <t>2026타인4296</t>
+  </si>
+  <si>
+    <t>2026타인4297</t>
+  </si>
+  <si>
+    <t>2026타인4298</t>
+  </si>
+  <si>
+    <t>2026타인4299</t>
+  </si>
+  <si>
+    <t>2026타인4300</t>
+  </si>
+  <si>
+    <t>2026타인4301</t>
+  </si>
+  <si>
+    <t>2026타인4302</t>
+  </si>
+  <si>
+    <t>2026타인4309</t>
+  </si>
+  <si>
+    <t>2026타인100260</t>
+  </si>
+  <si>
+    <t>2026타인100261</t>
+  </si>
+  <si>
+    <t>2026타인10388</t>
+  </si>
+  <si>
+    <t>2026타인10389</t>
+  </si>
+  <si>
+    <t>2026타인10390</t>
+  </si>
+  <si>
+    <t>2026타인10397</t>
+  </si>
+  <si>
+    <t>2026타인10398</t>
+  </si>
+  <si>
+    <t>2026타인10399</t>
+  </si>
+  <si>
+    <t>2026타인10404</t>
+  </si>
+  <si>
+    <t>2026타인10405</t>
+  </si>
+  <si>
+    <t>2026타인10408</t>
+  </si>
+  <si>
+    <t>2026타인10414</t>
+  </si>
+  <si>
+    <t>2026타인10416</t>
+  </si>
+  <si>
+    <t>2026타인10417</t>
+  </si>
+  <si>
+    <t>2026타인10419</t>
+  </si>
+  <si>
+    <t>2026타인10420</t>
+  </si>
+  <si>
+    <t>2026타인10361</t>
+  </si>
+  <si>
+    <t>2026타인4303</t>
+  </si>
+  <si>
+    <t>2026타인4305</t>
+  </si>
+  <si>
+    <t>2026타인4307</t>
+  </si>
+  <si>
+    <t>2026타인4310</t>
+  </si>
+  <si>
+    <t>2026타인10256</t>
+  </si>
+  <si>
+    <t>2026타인100258</t>
+  </si>
+  <si>
+    <t>2026타인10386</t>
+  </si>
+  <si>
+    <t>2026타인10391</t>
+  </si>
+  <si>
+    <t>2026타인10393</t>
+  </si>
+  <si>
+    <t>2026타인10395</t>
+  </si>
+  <si>
+    <t>2026타인10400</t>
+  </si>
+  <si>
+    <t>2026타인10402</t>
+  </si>
+  <si>
+    <t>2026타인10406</t>
+  </si>
+  <si>
+    <t>2026타인10409</t>
+  </si>
+  <si>
+    <t>2026타인10411</t>
+  </si>
+  <si>
+    <t>2026타인10362</t>
+  </si>
+  <si>
+    <t>2026타인4304</t>
+  </si>
+  <si>
+    <t>2026타인4306</t>
+  </si>
+  <si>
+    <t>2026타인4308</t>
+  </si>
+  <si>
+    <t>2026타인4311</t>
+  </si>
+  <si>
+    <t>2026타인10257</t>
+  </si>
+  <si>
+    <t>2026타인100259</t>
+  </si>
+  <si>
+    <t>2026타인10387</t>
+  </si>
+  <si>
+    <t>2026타인10392</t>
+  </si>
+  <si>
+    <t>2026타인10394</t>
+  </si>
+  <si>
+    <t>2026타인10396</t>
+  </si>
+  <si>
+    <t>2026타인10401</t>
+  </si>
+  <si>
+    <t>2026타인10403</t>
+  </si>
+  <si>
+    <t>2026타인10407</t>
+  </si>
+  <si>
+    <t>2026타인10410</t>
+  </si>
+  <si>
+    <t>2026타인10412</t>
   </si>
 </sst>
 </file>
@@ -607,11 +649,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC6190E-F6A8-4356-BDE2-6BB4C1AFDCC8}">
-  <dimension ref="A1:H360"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
@@ -630,73 +672,73 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -705,10 +747,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H8" s="4"/>
     </row>
@@ -717,533 +759,611 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="7"/>
+      <c r="B47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="7"/>
+      <c r="A48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="7"/>
+      <c r="A49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="7"/>
+      <c r="A50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="7"/>
+      <c r="A51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="7"/>
+      <c r="A52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="7"/>
+      <c r="A53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="7"/>
+      <c r="A54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="7"/>
+      <c r="A55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="7"/>
+      <c r="A56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="4"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="7"/>
+      <c r="A57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="7"/>
+      <c r="A58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="7"/>
+      <c r="A59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8">
@@ -1253,13 +1373,13 @@
       <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="4"/>
+      <c r="A61" s="9"/>
       <c r="B61" s="4"/>
       <c r="C61" s="7"/>
       <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="4"/>
+      <c r="A62" s="8"/>
       <c r="B62" s="4"/>
       <c r="C62" s="7"/>
       <c r="H62" s="4"/>
@@ -1278,25 +1398,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="4"/>
       <c r="C65" s="7"/>
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4"/>
-      <c r="B66" s="3"/>
+      <c r="B66" s="4"/>
       <c r="C66" s="7"/>
       <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="4"/>
       <c r="C67" s="7"/>
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="4"/>
       <c r="C68" s="7"/>
       <c r="H68" s="4"/>
     </row>
@@ -1377,12 +1497,12 @@
       <c r="C81" s="7"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="9"/>
+      <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="7"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="8"/>
+      <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="7"/>
     </row>
@@ -1658,7 +1778,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
+      <c r="B138" s="3"/>
       <c r="C138" s="7"/>
     </row>
     <row r="139" spans="1:3">
@@ -1728,7 +1848,6 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
       <c r="C152" s="7"/>
     </row>
     <row r="153" spans="1:3">
@@ -1742,8 +1861,7 @@
       <c r="C154" s="7"/>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
+      <c r="A155" s="8"/>
       <c r="C155" s="7"/>
     </row>
     <row r="156" spans="1:3">
@@ -1753,7 +1871,6 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
       <c r="C157" s="7"/>
     </row>
     <row r="158" spans="1:3">
@@ -1763,7 +1880,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="4"/>
-      <c r="B159" s="3"/>
+      <c r="B159" s="4"/>
       <c r="C159" s="7"/>
     </row>
     <row r="160" spans="1:3">
@@ -1788,7 +1905,6 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
       <c r="C164" s="7"/>
     </row>
     <row r="165" spans="1:3">
@@ -1803,7 +1919,6 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="4"/>
-      <c r="B167" s="4"/>
       <c r="C167" s="7"/>
     </row>
     <row r="168" spans="1:3">
@@ -1842,25 +1957,24 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="4"/>
-      <c r="B175" s="4"/>
       <c r="C175" s="7"/>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="8"/>
+      <c r="A176" s="4"/>
+      <c r="B176" s="4"/>
       <c r="C176" s="7"/>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
       <c r="C177" s="7"/>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="4"/>
+      <c r="B178" s="4"/>
       <c r="C178" s="7"/>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
       <c r="C179" s="7"/>
     </row>
     <row r="180" spans="1:3">
@@ -1870,22 +1984,20 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
       <c r="C181" s="7"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
+      <c r="B182" s="3"/>
       <c r="C182" s="7"/>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
       <c r="C183" s="7"/>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
+      <c r="B184" s="3"/>
       <c r="C184" s="7"/>
     </row>
     <row r="185" spans="1:3">
@@ -1894,16 +2006,16 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="4"/>
-      <c r="B186" s="4"/>
+      <c r="B186" s="2"/>
       <c r="C186" s="7"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
       <c r="C187" s="7"/>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="4"/>
+      <c r="B188" s="4"/>
       <c r="C188" s="7"/>
     </row>
     <row r="189" spans="1:3">
@@ -1942,6 +2054,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="4"/>
+      <c r="B196" s="4"/>
       <c r="C196" s="7"/>
     </row>
     <row r="197" spans="1:3">
@@ -1951,61 +2064,55 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="4"/>
+      <c r="B198" s="4"/>
       <c r="C198" s="7"/>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="7"/>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="4"/>
+      <c r="A200" s="3"/>
       <c r="C200" s="7"/>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="7"/>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="4"/>
+      <c r="A202" s="3"/>
+      <c r="B202" s="4"/>
       <c r="C202" s="7"/>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="4"/>
-      <c r="B203" s="3"/>
+      <c r="B203" s="4"/>
       <c r="C203" s="7"/>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204" s="4"/>
+      <c r="A204" s="2"/>
       <c r="C204" s="7"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="4"/>
-      <c r="B205" s="3"/>
+      <c r="B205" s="4"/>
       <c r="C205" s="7"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4"/>
+      <c r="B206" s="4"/>
       <c r="C206" s="7"/>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="4"/>
-      <c r="B207" s="2"/>
+      <c r="B207" s="4"/>
       <c r="C207" s="7"/>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
       <c r="C208" s="7"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="7"/>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="4"/>
-      <c r="B210" s="4"/>
       <c r="C210" s="7"/>
     </row>
     <row r="211" spans="1:3">
@@ -2014,26 +2121,21 @@
       <c r="C211" s="7"/>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="4"/>
-      <c r="B212" s="4"/>
       <c r="C212" s="7"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="7"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="7"/>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="4"/>
+      <c r="B215" s="4"/>
       <c r="C215" s="7"/>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="7"/>
     </row>
@@ -2043,12 +2145,9 @@
       <c r="C217" s="7"/>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
       <c r="C218" s="7"/>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="7"/>
     </row>
@@ -2056,66 +2155,68 @@
       <c r="B220" s="4"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="3"/>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="B222" s="4"/>
+      <c r="A221" s="4"/>
+      <c r="B221" s="4"/>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="3"/>
       <c r="B223" s="4"/>
     </row>
     <row r="224" spans="1:3">
       <c r="B224" s="4"/>
     </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="2"/>
-    </row>
     <row r="226" spans="1:2">
       <c r="B226" s="4"/>
     </row>
     <row r="227" spans="1:2">
+      <c r="A227" s="4"/>
       <c r="B227" s="4"/>
     </row>
     <row r="228" spans="1:2">
       <c r="B228" s="4"/>
     </row>
     <row r="229" spans="1:2">
+      <c r="A229" s="4"/>
       <c r="B229" s="4"/>
     </row>
     <row r="230" spans="1:2">
       <c r="B230" s="4"/>
     </row>
+    <row r="231" spans="1:2">
+      <c r="B231" s="4"/>
+    </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="4"/>
       <c r="B232" s="4"/>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="B233" s="4"/>
     </row>
     <row r="234" spans="1:2">
       <c r="B234" s="4"/>
     </row>
     <row r="235" spans="1:2">
+      <c r="A235" s="4"/>
       <c r="B235" s="4"/>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="B236" s="4"/>
     </row>
     <row r="237" spans="1:2">
       <c r="B237" s="4"/>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="4"/>
       <c r="B238" s="4"/>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="4"/>
+      <c r="B239" s="4"/>
     </row>
     <row r="240" spans="1:2">
       <c r="B240" s="4"/>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="B241" s="4"/>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
     </row>
+    <row r="243" spans="1:2">
+      <c r="B243" s="4"/>
+    </row>
     <row r="244" spans="1:2">
       <c r="B244" s="4"/>
     </row>
@@ -2126,23 +2227,16 @@
       <c r="B247" s="4"/>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="4"/>
       <c r="B248" s="4"/>
     </row>
-    <row r="249" spans="1:2">
-      <c r="B249" s="4"/>
-    </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="4"/>
       <c r="B250" s="4"/>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="B251" s="4"/>
     </row>
     <row r="252" spans="1:2">
       <c r="B252" s="4"/>
     </row>
     <row r="253" spans="1:2">
+      <c r="A253" s="4"/>
       <c r="B253" s="4"/>
     </row>
     <row r="254" spans="1:2">
@@ -2152,55 +2246,57 @@
       <c r="B255" s="4"/>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="4"/>
       <c r="B256" s="4"/>
     </row>
+    <row r="257" spans="1:2">
+      <c r="B257" s="4"/>
+    </row>
     <row r="258" spans="1:2">
+      <c r="A258" s="4"/>
       <c r="B258" s="4"/>
     </row>
-    <row r="259" spans="1:2">
-      <c r="B259" s="4"/>
-    </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="4"/>
       <c r="B260" s="4"/>
     </row>
     <row r="261" spans="1:2">
       <c r="B261" s="4"/>
     </row>
+    <row r="262" spans="1:2">
+      <c r="B262" s="4"/>
+    </row>
     <row r="263" spans="1:2">
       <c r="A263" s="4"/>
-      <c r="B263" s="4"/>
     </row>
     <row r="264" spans="1:2">
       <c r="B264" s="4"/>
     </row>
-    <row r="265" spans="1:2">
-      <c r="B265" s="4"/>
-    </row>
     <row r="266" spans="1:2">
+      <c r="A266" s="4"/>
       <c r="B266" s="4"/>
     </row>
+    <row r="267" spans="1:2">
+      <c r="B267" s="4"/>
+    </row>
     <row r="268" spans="1:2">
-      <c r="B268" s="4"/>
+      <c r="A268" s="4"/>
     </row>
     <row r="269" spans="1:2">
       <c r="B269" s="4"/>
     </row>
-    <row r="271" spans="1:2">
-      <c r="B271" s="4"/>
-    </row>
-    <row r="273" spans="1:2">
-      <c r="B273" s="4"/>
+    <row r="270" spans="1:2">
+      <c r="B270" s="4"/>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="B272" s="4"/>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="4"/>
       <c r="B274" s="4"/>
     </row>
     <row r="275" spans="1:2">
       <c r="B275" s="4"/>
     </row>
     <row r="276" spans="1:2">
+      <c r="A276" s="4"/>
       <c r="B276" s="4"/>
     </row>
     <row r="277" spans="1:2">
@@ -2210,74 +2306,65 @@
       <c r="B278" s="4"/>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="4"/>
       <c r="B279" s="4"/>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="4"/>
     </row>
     <row r="281" spans="1:2">
       <c r="B281" s="4"/>
     </row>
     <row r="282" spans="1:2">
+      <c r="A282" s="4"/>
       <c r="B282" s="4"/>
     </row>
-    <row r="283" spans="1:2">
-      <c r="B283" s="4"/>
-    </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="4"/>
+      <c r="B284" s="4"/>
     </row>
     <row r="285" spans="1:2">
+      <c r="A285" s="4"/>
       <c r="B285" s="4"/>
     </row>
+    <row r="286" spans="1:2">
+      <c r="B286" s="4"/>
+    </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="4"/>
       <c r="B287" s="4"/>
     </row>
     <row r="288" spans="1:2">
+      <c r="A288" s="4"/>
       <c r="B288" s="4"/>
     </row>
-    <row r="289" spans="1:2">
-      <c r="A289" s="4"/>
-    </row>
     <row r="290" spans="1:2">
+      <c r="A290" s="4"/>
       <c r="B290" s="4"/>
     </row>
-    <row r="291" spans="1:2">
-      <c r="B291" s="4"/>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="B293" s="4"/>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="B295" s="4"/>
+    <row r="292" spans="1:2">
+      <c r="B292" s="4"/>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="B294" s="4"/>
     </row>
     <row r="296" spans="1:2">
       <c r="B296" s="4"/>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="4"/>
-      <c r="B297" s="4"/>
     </row>
     <row r="298" spans="1:2">
-      <c r="B298" s="4"/>
+      <c r="B298" s="3"/>
     </row>
     <row r="299" spans="1:2">
-      <c r="B299" s="4"/>
+      <c r="B299" s="3"/>
     </row>
     <row r="300" spans="1:2">
-      <c r="B300" s="4"/>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" s="4"/>
+      <c r="A300" s="4"/>
     </row>
     <row r="302" spans="1:2">
       <c r="B302" s="4"/>
     </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="4"/>
-      <c r="B303" s="4"/>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="B305" s="4"/>
+    <row r="304" spans="1:2">
+      <c r="B304" s="4"/>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="4"/>
@@ -2287,118 +2374,73 @@
       <c r="B307" s="4"/>
     </row>
     <row r="308" spans="1:2">
-      <c r="B308" s="4"/>
+      <c r="A308" s="4"/>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="4"/>
       <c r="B309" s="4"/>
     </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="4"/>
+      <c r="B310" s="4"/>
+    </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="4"/>
       <c r="B311" s="4"/>
     </row>
-    <row r="313" spans="1:2">
-      <c r="B313" s="4"/>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="B315" s="4"/>
+    <row r="312" spans="1:2">
+      <c r="A312" s="4"/>
+      <c r="B312" s="4"/>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="4"/>
+      <c r="B314" s="4"/>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="B316" s="4"/>
     </row>
     <row r="317" spans="1:2">
-      <c r="B317" s="4"/>
+      <c r="A317" s="3"/>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="4"/>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="B319" s="3"/>
+      <c r="A318" s="3"/>
+      <c r="B318" s="4"/>
     </row>
     <row r="320" spans="1:2">
-      <c r="B320" s="3"/>
+      <c r="A320" s="4"/>
+      <c r="B320" s="4"/>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="4"/>
-    </row>
-    <row r="323" spans="1:2">
-      <c r="B323" s="4"/>
+      <c r="B321" s="4"/>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="4"/>
+      <c r="B322" s="4"/>
     </row>
     <row r="325" spans="1:2">
-      <c r="B325" s="4"/>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="4"/>
-      <c r="B327" s="4"/>
-    </row>
-    <row r="328" spans="1:2">
-      <c r="B328" s="4"/>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="4"/>
+      <c r="A325" s="4"/>
     </row>
     <row r="330" spans="1:2">
-      <c r="B330" s="4"/>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="4"/>
-      <c r="B331" s="4"/>
+      <c r="A330" s="4"/>
     </row>
     <row r="332" spans="1:2">
-      <c r="B332" s="4"/>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" s="4"/>
-      <c r="B333" s="4"/>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" s="4"/>
-      <c r="B335" s="4"/>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="B337" s="4"/>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" s="3"/>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="3"/>
-      <c r="B339" s="4"/>
-    </row>
-    <row r="341" spans="1:2">
-      <c r="A341" s="4"/>
-      <c r="B341" s="4"/>
-    </row>
-    <row r="342" spans="1:2">
-      <c r="B342" s="4"/>
-    </row>
-    <row r="343" spans="1:2">
-      <c r="A343" s="4"/>
-      <c r="B343" s="4"/>
-    </row>
-    <row r="346" spans="1:2">
-      <c r="A346" s="4"/>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" s="4"/>
-    </row>
-    <row r="353" spans="1:1">
-      <c r="A353" s="4"/>
-    </row>
-    <row r="355" spans="1:1">
-      <c r="A355" s="4"/>
-    </row>
-    <row r="357" spans="1:1">
-      <c r="A357" s="4"/>
-    </row>
-    <row r="360" spans="1:1">
-      <c r="A360" s="6"/>
+      <c r="A332" s="4"/>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="4"/>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="4"/>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C360" xr:uid="{C9EB9D7D-12FD-4816-92B0-7F8FD3F3875E}">
-    <sortState ref="A2:C301">
+    <sortState ref="A2:C280">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:C46">
-    <sortCondition ref="B9"/>
+  <sortState ref="A2:C59">
+    <sortCondition ref="B12"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
